--- a/platform_PiN_output/Myanmar___MMR/ocha_figures_Myanmar___MMR_0908_09AM.xlsx
+++ b/platform_PiN_output/Myanmar___MMR/ocha_figures_Myanmar___MMR_0908_09AM.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ocha_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mismatch_ocha_data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,25 +498,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>297032.6666666667</v>
+        <v>96433.7655254244</v>
       </c>
       <c r="D2" t="n">
-        <v>153041.7777777777</v>
+        <v>49686.10045297931</v>
       </c>
       <c r="E2" t="n">
-        <v>143990.888888889</v>
+        <v>46747.6650724451</v>
       </c>
       <c r="F2" t="n">
-        <v>22848.66666666667</v>
+        <v>7417.981963494185</v>
       </c>
       <c r="G2" t="n">
-        <v>253842.3333333334</v>
+        <v>82411.71695961597</v>
       </c>
       <c r="H2" t="n">
-        <v>38348.55555555555</v>
+        <v>12450.13101145942</v>
       </c>
       <c r="I2" t="n">
-        <v>4841.777777777777</v>
+        <v>1571.917554349014</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
@@ -534,25 +535,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>93244.66666666667</v>
+        <v>34138.65118644677</v>
       </c>
       <c r="D3" t="n">
-        <v>46633.16666666671</v>
+        <v>17073.2918832116</v>
       </c>
       <c r="E3" t="n">
-        <v>46611.49999999996</v>
+        <v>17065.35930323517</v>
       </c>
       <c r="F3" t="n">
-        <v>7172.666666666667</v>
+        <v>2626.050091265136</v>
       </c>
       <c r="G3" t="n">
-        <v>43746.44444444445</v>
+        <v>16016.4078110222</v>
       </c>
       <c r="H3" t="n">
-        <v>41364.55555555556</v>
+        <v>15144.35285228299</v>
       </c>
       <c r="I3" t="n">
-        <v>8133.666666666667</v>
+        <v>2977.890523141583</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
@@ -571,22 +572,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>606.6666666666666</v>
+        <v>226.7777777777779</v>
       </c>
       <c r="D4" t="n">
-        <v>271.5555555555558</v>
+        <v>101.510052910053</v>
       </c>
       <c r="E4" t="n">
-        <v>335.1111111111109</v>
+        <v>125.2677248677248</v>
       </c>
       <c r="F4" t="n">
-        <v>46.66666666666666</v>
+        <v>17.44444444444445</v>
       </c>
       <c r="G4" t="n">
-        <v>108.3333333333333</v>
+        <v>40.49603174603177</v>
       </c>
       <c r="H4" t="n">
-        <v>498.3333333333333</v>
+        <v>186.2817460317461</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -608,25 +609,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52753.27777777777</v>
+        <v>18002.11111111113</v>
       </c>
       <c r="D5" t="n">
-        <v>24524.49999999997</v>
+        <v>8369.011226263981</v>
       </c>
       <c r="E5" t="n">
-        <v>28228.7777777778</v>
+        <v>9633.09988484715</v>
       </c>
       <c r="F5" t="n">
-        <v>4057.944444444444</v>
+        <v>1384.777777777779</v>
       </c>
       <c r="G5" t="n">
-        <v>51285.72222222222</v>
+        <v>17501.30624578827</v>
       </c>
       <c r="H5" t="n">
-        <v>941.7777777777777</v>
+        <v>321.3826497938052</v>
       </c>
       <c r="I5" t="n">
-        <v>525.7777777777777</v>
+        <v>179.4222155290569</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
@@ -645,25 +646,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16922.38888888889</v>
+        <v>7583.980679215218</v>
       </c>
       <c r="D6" t="n">
-        <v>8174.833333333327</v>
+        <v>3663.654018524049</v>
       </c>
       <c r="E6" t="n">
-        <v>8747.55555555556</v>
+        <v>3920.326660691169</v>
       </c>
       <c r="F6" t="n">
-        <v>1301.722222222222</v>
+        <v>583.3831291704014</v>
       </c>
       <c r="G6" t="n">
-        <v>13080.88888888889</v>
+        <v>5862.364306343989</v>
       </c>
       <c r="H6" t="n">
-        <v>2398.5</v>
+        <v>1074.917836868838</v>
       </c>
       <c r="I6" t="n">
-        <v>1443</v>
+        <v>646.6985360023903</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
@@ -682,22 +683,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5535.833333333333</v>
+        <v>2560.94599591109</v>
       </c>
       <c r="D7" t="n">
-        <v>2672.222222222223</v>
+        <v>1236.203546623749</v>
       </c>
       <c r="E7" t="n">
-        <v>2863.61111111111</v>
+        <v>1324.742449287341</v>
       </c>
       <c r="F7" t="n">
-        <v>425.8333333333333</v>
+        <v>196.9958458393146</v>
       </c>
       <c r="G7" t="n">
-        <v>4925.555555555555</v>
+        <v>2278.623834587558</v>
       </c>
       <c r="H7" t="n">
-        <v>610.2777777777777</v>
+        <v>282.3221613235318</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -719,25 +720,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>186039.3888888889</v>
+        <v>61796.70202331954</v>
       </c>
       <c r="D8" t="n">
-        <v>95525.44444444451</v>
+        <v>31730.68596513254</v>
       </c>
       <c r="E8" t="n">
-        <v>90513.94444444439</v>
+        <v>30066.016058187</v>
       </c>
       <c r="F8" t="n">
-        <v>14310.72222222222</v>
+        <v>4753.592463332272</v>
       </c>
       <c r="G8" t="n">
-        <v>178955.8333333333</v>
+        <v>59443.75744235375</v>
       </c>
       <c r="H8" t="n">
-        <v>4310.944444444444</v>
+        <v>1431.966374774137</v>
       </c>
       <c r="I8" t="n">
-        <v>2772.611111111111</v>
+        <v>920.9782061916422</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
@@ -756,25 +757,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>116546.4444444445</v>
+        <v>39911.19712026726</v>
       </c>
       <c r="D9" t="n">
-        <v>60503.44444444445</v>
+        <v>20719.33561927267</v>
       </c>
       <c r="E9" t="n">
-        <v>56043.00000000001</v>
+        <v>19191.86150099459</v>
       </c>
       <c r="F9" t="n">
-        <v>8965.111111111111</v>
+        <v>3070.092086174405</v>
       </c>
       <c r="G9" t="n">
-        <v>111038.0555555556</v>
+        <v>38024.85562089762</v>
       </c>
       <c r="H9" t="n">
-        <v>4687.944444444444</v>
+        <v>1605.381234090517</v>
       </c>
       <c r="I9" t="n">
-        <v>820.4444444444446</v>
+        <v>280.960265279129</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
@@ -793,25 +794,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>288073.5</v>
+        <v>70410.16666666669</v>
       </c>
       <c r="D10" t="n">
-        <v>105587.4444444443</v>
+        <v>25807.40526719999</v>
       </c>
       <c r="E10" t="n">
-        <v>182486.0555555557</v>
+        <v>44602.7613994667</v>
       </c>
       <c r="F10" t="n">
-        <v>22159.5</v>
+        <v>5416.166666666668</v>
       </c>
       <c r="G10" t="n">
-        <v>276589.4444444444</v>
+        <v>67603.26403356811</v>
       </c>
       <c r="H10" t="n">
-        <v>8439.888888888889</v>
+        <v>2062.85542861393</v>
       </c>
       <c r="I10" t="n">
-        <v>3044.166666666667</v>
+        <v>744.0472044846581</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
@@ -830,25 +831,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>122738.0555555555</v>
+        <v>39718.35631489512</v>
       </c>
       <c r="D11" t="n">
-        <v>62467.88888888896</v>
+        <v>20214.77249169168</v>
       </c>
       <c r="E11" t="n">
-        <v>60270.16666666659</v>
+        <v>19503.58382320344</v>
       </c>
       <c r="F11" t="n">
-        <v>9441.388888888889</v>
+        <v>3055.258178068856</v>
       </c>
       <c r="G11" t="n">
-        <v>95961.66666666666</v>
+        <v>31053.44672429383</v>
       </c>
       <c r="H11" t="n">
-        <v>8502.722222222221</v>
+        <v>2751.503185708672</v>
       </c>
       <c r="I11" t="n">
-        <v>18273.66666666667</v>
+        <v>5913.40640489262</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
@@ -867,25 +868,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>85838.27777777778</v>
+        <v>29754.36145701282</v>
       </c>
       <c r="D12" t="n">
-        <v>43097.16666666666</v>
+        <v>14938.89099328015</v>
       </c>
       <c r="E12" t="n">
-        <v>42741.11111111112</v>
+        <v>14815.47046373267</v>
       </c>
       <c r="F12" t="n">
-        <v>6602.944444444444</v>
+        <v>2288.797035154832</v>
       </c>
       <c r="G12" t="n">
-        <v>63882.00000000001</v>
+        <v>22143.59569885235</v>
       </c>
       <c r="H12" t="n">
-        <v>19383</v>
+        <v>6718.783310335542</v>
       </c>
       <c r="I12" t="n">
-        <v>2573.277777777778</v>
+        <v>891.9824478249324</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
@@ -904,25 +905,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50602.5</v>
+        <v>16889.8888888889</v>
       </c>
       <c r="D13" t="n">
-        <v>25396.94444444443</v>
+        <v>8476.884932245455</v>
       </c>
       <c r="E13" t="n">
-        <v>25205.55555555557</v>
+        <v>8413.003956643446</v>
       </c>
       <c r="F13" t="n">
-        <v>3892.5</v>
+        <v>1299.222222222223</v>
       </c>
       <c r="G13" t="n">
-        <v>1372.222222222222</v>
+        <v>458.0145420522217</v>
       </c>
       <c r="H13" t="n">
-        <v>47101.16666666666</v>
+        <v>15721.22862579986</v>
       </c>
       <c r="I13" t="n">
-        <v>2129.111111111111</v>
+        <v>710.6457210368155</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
@@ -941,25 +942,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>49956.83333333334</v>
+        <v>16815.75019397499</v>
       </c>
       <c r="D14" t="n">
-        <v>25266.94444444447</v>
+        <v>8504.995164681954</v>
       </c>
       <c r="E14" t="n">
-        <v>24689.88888888887</v>
+        <v>8310.755029293032</v>
       </c>
       <c r="F14" t="n">
-        <v>3842.833333333333</v>
+        <v>1293.519245690384</v>
       </c>
       <c r="G14" t="n">
-        <v>5751.777777777778</v>
+        <v>1936.080648607318</v>
       </c>
       <c r="H14" t="n">
-        <v>41355.88888888889</v>
+        <v>13920.62407088803</v>
       </c>
       <c r="I14" t="n">
-        <v>2849.166666666667</v>
+        <v>959.0454744796421</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
@@ -978,19 +979,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>52989.44444444445</v>
+        <v>21231.59951176592</v>
       </c>
       <c r="D15" t="n">
-        <v>26639.88888888886</v>
+        <v>10673.96455759843</v>
       </c>
       <c r="E15" t="n">
-        <v>26349.55555555558</v>
+        <v>10557.63495416749</v>
       </c>
       <c r="F15" t="n">
-        <v>4076.111111111111</v>
+        <v>1633.199962443532</v>
       </c>
       <c r="G15" t="n">
-        <v>52989.44444444445</v>
+        <v>21231.59951176592</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1015,25 +1016,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2694.611111111111</v>
+        <v>1035.716306129137</v>
       </c>
       <c r="D16" t="n">
-        <v>1323.822238634498</v>
+        <v>508.8319695990411</v>
       </c>
       <c r="E16" t="n">
-        <v>1370.788872476613</v>
+        <v>526.8843365300957</v>
       </c>
       <c r="F16" t="n">
-        <v>207.2777777777778</v>
+        <v>79.67048508685667</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1991.166666666666</v>
+        <v>765.3363323500481</v>
       </c>
       <c r="I16" t="n">
-        <v>703.4444444444443</v>
+        <v>270.3799737790885</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
@@ -1052,19 +1053,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7819.5</v>
+        <v>3052.55139453269</v>
       </c>
       <c r="D17" t="n">
-        <v>3840.777777777776</v>
+        <v>1499.350541805194</v>
       </c>
       <c r="E17" t="n">
-        <v>3978.722222222224</v>
+        <v>1553.200852727496</v>
       </c>
       <c r="F17" t="n">
-        <v>601.5</v>
+        <v>234.8116457332839</v>
       </c>
       <c r="G17" t="n">
-        <v>7819.5</v>
+        <v>3052.55139453269</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1089,19 +1090,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6275.388888888889</v>
+        <v>2580.203049482164</v>
       </c>
       <c r="D18" t="n">
-        <v>3066.555555555557</v>
+        <v>1260.851898734178</v>
       </c>
       <c r="E18" t="n">
-        <v>3208.833333333331</v>
+        <v>1319.351150747986</v>
       </c>
       <c r="F18" t="n">
-        <v>482.7222222222222</v>
+        <v>198.4771576524741</v>
       </c>
       <c r="G18" t="n">
-        <v>6275.388888888889</v>
+        <v>2580.203049482164</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1126,19 +1127,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10010.72222222222</v>
+        <v>3563.860431942939</v>
       </c>
       <c r="D19" t="n">
-        <v>4953.000000000003</v>
+        <v>1763.289433826181</v>
       </c>
       <c r="E19" t="n">
-        <v>5057.72222222222</v>
+        <v>1800.570998116759</v>
       </c>
       <c r="F19" t="n">
-        <v>770.0555555555555</v>
+        <v>274.1431101494568</v>
       </c>
       <c r="G19" t="n">
-        <v>10010.72222222222</v>
+        <v>3563.860431942939</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1163,25 +1164,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>79506.55555555555</v>
+        <v>26781.6801074292</v>
       </c>
       <c r="D20" t="n">
-        <v>40418.44444444444</v>
+        <v>13614.90058256425</v>
       </c>
       <c r="E20" t="n">
-        <v>39088.11111111111</v>
+        <v>13166.77952486495</v>
       </c>
       <c r="F20" t="n">
-        <v>6115.888888888889</v>
+        <v>2060.129239033015</v>
       </c>
       <c r="G20" t="n">
-        <v>41865.05555555555</v>
+        <v>14102.18965887896</v>
       </c>
       <c r="H20" t="n">
-        <v>35148.38888888888</v>
+        <v>11839.68920469684</v>
       </c>
       <c r="I20" t="n">
-        <v>2493.111111111111</v>
+        <v>839.801243853402</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
@@ -1200,25 +1201,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>70157.38888888889</v>
+        <v>28364.69378762348</v>
       </c>
       <c r="D21" t="n">
-        <v>35713.16666666664</v>
+        <v>14438.86456907168</v>
       </c>
       <c r="E21" t="n">
-        <v>34444.22222222226</v>
+        <v>13925.8292185518</v>
       </c>
       <c r="F21" t="n">
-        <v>5396.722222222223</v>
+        <v>2181.899522124883</v>
       </c>
       <c r="G21" t="n">
-        <v>25105.88888888889</v>
+        <v>10150.3328712425</v>
       </c>
       <c r="H21" t="n">
-        <v>44077.94444444445</v>
+        <v>17820.75155240782</v>
       </c>
       <c r="I21" t="n">
-        <v>973.5555555555557</v>
+        <v>393.609363973157</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
@@ -1237,25 +1238,25 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29311.38888888889</v>
+        <v>11841.1250944543</v>
       </c>
       <c r="D22" t="n">
-        <v>14929.77777777778</v>
+        <v>6031.285892634207</v>
       </c>
       <c r="E22" t="n">
-        <v>14381.61111111111</v>
+        <v>5809.839201820094</v>
       </c>
       <c r="F22" t="n">
-        <v>2254.722222222222</v>
+        <v>910.8557764964846</v>
       </c>
       <c r="G22" t="n">
-        <v>19031.27777777777</v>
+        <v>7688.197298607004</v>
       </c>
       <c r="H22" t="n">
-        <v>10108.94444444444</v>
+        <v>4083.780410178067</v>
       </c>
       <c r="I22" t="n">
-        <v>171.1666666666667</v>
+        <v>69.14738566922925</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
@@ -1274,25 +1275,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6406.111111111111</v>
+        <v>2506.676314338695</v>
       </c>
       <c r="D23" t="n">
-        <v>3216.055555555554</v>
+        <v>1258.42498621761</v>
       </c>
       <c r="E23" t="n">
-        <v>3190.055555555557</v>
+        <v>1248.251328121085</v>
       </c>
       <c r="F23" t="n">
-        <v>492.7777777777778</v>
+        <v>192.8212549491304</v>
       </c>
       <c r="G23" t="n">
-        <v>2744.444444444444</v>
+        <v>1073.886132411166</v>
       </c>
       <c r="H23" t="n">
-        <v>3336.666666666667</v>
+        <v>1305.619455720944</v>
       </c>
       <c r="I23" t="n">
-        <v>325</v>
+        <v>127.1707262065854</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
@@ -1311,25 +1312,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8008.722222222222</v>
+        <v>2556.636112614509</v>
       </c>
       <c r="D24" t="n">
-        <v>3576.444444444447</v>
+        <v>1141.713592719547</v>
       </c>
       <c r="E24" t="n">
-        <v>4432.277777777775</v>
+        <v>1414.922519894962</v>
       </c>
       <c r="F24" t="n">
-        <v>616.0555555555555</v>
+        <v>196.6643163549623</v>
       </c>
       <c r="G24" t="n">
-        <v>6523.11111111111</v>
+        <v>2082.382304007057</v>
       </c>
       <c r="H24" t="n">
-        <v>1300</v>
+        <v>415.0009020386073</v>
       </c>
       <c r="I24" t="n">
-        <v>185.6111111111111</v>
+        <v>59.25290656884561</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
@@ -1348,22 +1349,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21338.77777777778</v>
+        <v>7626.202557304303</v>
       </c>
       <c r="D25" t="n">
-        <v>9684.277777777786</v>
+        <v>3461.03533780862</v>
       </c>
       <c r="E25" t="n">
-        <v>11654.49999999999</v>
+        <v>4165.167219495683</v>
       </c>
       <c r="F25" t="n">
-        <v>1641.444444444444</v>
+        <v>586.6309659464848</v>
       </c>
       <c r="G25" t="n">
-        <v>19797.55555555555</v>
+        <v>7075.389714371677</v>
       </c>
       <c r="H25" t="n">
-        <v>1541.222222222222</v>
+        <v>550.8128429326265</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1385,25 +1386,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9713.166666666666</v>
+        <v>3461.918532292055</v>
       </c>
       <c r="D26" t="n">
-        <v>4656.166666666664</v>
+        <v>1659.527755051444</v>
       </c>
       <c r="E26" t="n">
-        <v>5057.000000000002</v>
+        <v>1802.390777240611</v>
       </c>
       <c r="F26" t="n">
-        <v>747.1666666666666</v>
+        <v>266.3014255609273</v>
       </c>
       <c r="G26" t="n">
-        <v>2513.333333333333</v>
+        <v>895.7897607536881</v>
       </c>
       <c r="H26" t="n">
-        <v>5881.777777777777</v>
+        <v>2096.353968844263</v>
       </c>
       <c r="I26" t="n">
-        <v>1318.055555555555</v>
+        <v>469.7748026941037</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
@@ -1422,25 +1423,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>359603.8333333333</v>
+        <v>121046.1390946941</v>
       </c>
       <c r="D27" t="n">
-        <v>187238.2777777776</v>
+        <v>63026.22084323304</v>
       </c>
       <c r="E27" t="n">
-        <v>172365.5555555557</v>
+        <v>58019.91825146101</v>
       </c>
       <c r="F27" t="n">
-        <v>27661.83333333333</v>
+        <v>9311.24146882262</v>
       </c>
       <c r="G27" t="n">
-        <v>321395.3888888889</v>
+        <v>108184.8060050465</v>
       </c>
       <c r="H27" t="n">
-        <v>34889.11111111111</v>
+        <v>11744.01328622968</v>
       </c>
       <c r="I27" t="n">
-        <v>3319.333333333333</v>
+        <v>1117.319803417894</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
@@ -1459,25 +1460,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>219775.1111111111</v>
+        <v>80995.77777777785</v>
       </c>
       <c r="D28" t="n">
-        <v>113092.7777777778</v>
+        <v>41679.13942052105</v>
       </c>
       <c r="E28" t="n">
-        <v>106682.3333333333</v>
+        <v>39316.63835725681</v>
       </c>
       <c r="F28" t="n">
-        <v>16905.77777777778</v>
+        <v>6230.44444444445</v>
       </c>
       <c r="G28" t="n">
-        <v>189259.7777777778</v>
+        <v>69749.67650186078</v>
       </c>
       <c r="H28" t="n">
-        <v>27232.11111111111</v>
+        <v>10036.10467456521</v>
       </c>
       <c r="I28" t="n">
-        <v>3283.222222222222</v>
+        <v>1209.996601351866</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
@@ -1496,22 +1497,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>40427.83333333334</v>
+        <v>14884.27777777778</v>
       </c>
       <c r="D29" t="n">
-        <v>19738.33333333333</v>
+        <v>7267.043815614744</v>
       </c>
       <c r="E29" t="n">
-        <v>20689.50000000001</v>
+        <v>7617.233962163034</v>
       </c>
       <c r="F29" t="n">
-        <v>3109.833333333333</v>
+        <v>1144.944444444444</v>
       </c>
       <c r="G29" t="n">
-        <v>3179.222222222222</v>
+        <v>1170.491287096089</v>
       </c>
       <c r="H29" t="n">
-        <v>37248.61111111112</v>
+        <v>13713.78649068169</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1533,25 +1534,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>66459.61111111111</v>
+        <v>25410.39052980085</v>
       </c>
       <c r="D30" t="n">
-        <v>32774.44444444444</v>
+        <v>12531.09097099969</v>
       </c>
       <c r="E30" t="n">
-        <v>33685.16666666667</v>
+        <v>12879.29955880116</v>
       </c>
       <c r="F30" t="n">
-        <v>5112.277777777777</v>
+        <v>1954.645425369296</v>
       </c>
       <c r="G30" t="n">
-        <v>45520.94444444444</v>
+        <v>17404.63051589113</v>
       </c>
       <c r="H30" t="n">
-        <v>19806.22222222222</v>
+        <v>7572.777408300917</v>
       </c>
       <c r="I30" t="n">
-        <v>1132.444444444444</v>
+        <v>432.9826056088039</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
@@ -1570,22 +1571,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>170476.9444444444</v>
+        <v>56354.74928449043</v>
       </c>
       <c r="D31" t="n">
-        <v>83829.05555555561</v>
+        <v>27711.46223898025</v>
       </c>
       <c r="E31" t="n">
-        <v>86647.88888888883</v>
+        <v>28643.28704551018</v>
       </c>
       <c r="F31" t="n">
-        <v>13113.61111111111</v>
+        <v>4334.980714191572</v>
       </c>
       <c r="G31" t="n">
-        <v>143439.1111111111</v>
+        <v>47416.82325782828</v>
       </c>
       <c r="H31" t="n">
-        <v>27037.83333333333</v>
+        <v>8937.926026662155</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1607,25 +1608,25 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>108842.5</v>
+        <v>37087.27735681301</v>
       </c>
       <c r="D32" t="n">
-        <v>57187.72222222218</v>
+        <v>19486.29363952438</v>
       </c>
       <c r="E32" t="n">
-        <v>51654.77777777782</v>
+        <v>17600.98371728863</v>
       </c>
       <c r="F32" t="n">
-        <v>8372.5</v>
+        <v>2852.867488985616</v>
       </c>
       <c r="G32" t="n">
-        <v>73453.61111111111</v>
+        <v>25028.77504777324</v>
       </c>
       <c r="H32" t="n">
-        <v>35265.38888888888</v>
+        <v>12016.42059690005</v>
       </c>
       <c r="I32" t="n">
-        <v>123.5</v>
+        <v>42.08171213971019</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
@@ -1644,25 +1645,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>194331.2222222222</v>
+        <v>70397.62725964468</v>
       </c>
       <c r="D33" t="n">
-        <v>98623.05555555561</v>
+        <v>35726.78144466126</v>
       </c>
       <c r="E33" t="n">
-        <v>95708.16666666661</v>
+        <v>34670.84581498342</v>
       </c>
       <c r="F33" t="n">
-        <v>14948.55555555555</v>
+        <v>5415.202096895745</v>
       </c>
       <c r="G33" t="n">
-        <v>149999.7777777778</v>
+        <v>54338.30099084312</v>
       </c>
       <c r="H33" t="n">
-        <v>41171.72222222222</v>
+        <v>14914.69832533268</v>
       </c>
       <c r="I33" t="n">
-        <v>3159.722222222223</v>
+        <v>1144.62794346888</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
@@ -1681,25 +1682,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>41002</v>
+        <v>16946.64594085217</v>
       </c>
       <c r="D34" t="n">
-        <v>20997.16666666668</v>
+        <v>8678.394938321628</v>
       </c>
       <c r="E34" t="n">
-        <v>20004.83333333332</v>
+        <v>8268.251002530546</v>
       </c>
       <c r="F34" t="n">
-        <v>3154</v>
+        <v>1303.588149296321</v>
       </c>
       <c r="G34" t="n">
-        <v>27136.77777777778</v>
+        <v>11215.97397628372</v>
       </c>
       <c r="H34" t="n">
-        <v>13372.66666666667</v>
+        <v>5527.092514634307</v>
       </c>
       <c r="I34" t="n">
-        <v>492.5555555555555</v>
+        <v>203.5794499341433</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
@@ -1718,25 +1719,25 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38128.27777777777</v>
+        <v>15166.95395767034</v>
       </c>
       <c r="D35" t="n">
-        <v>20114.61111111112</v>
+        <v>8001.341743698541</v>
       </c>
       <c r="E35" t="n">
-        <v>18013.66666666665</v>
+        <v>7165.612213971804</v>
       </c>
       <c r="F35" t="n">
-        <v>2932.944444444444</v>
+        <v>1166.688765974642</v>
       </c>
       <c r="G35" t="n">
-        <v>29397.33333333333</v>
+        <v>11693.89301409304</v>
       </c>
       <c r="H35" t="n">
-        <v>8428.333333333332</v>
+        <v>3352.686013032275</v>
       </c>
       <c r="I35" t="n">
-        <v>302.6111111111111</v>
+        <v>120.374930545032</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
@@ -1755,25 +1756,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39459.33333333334</v>
+        <v>17698.85211757385</v>
       </c>
       <c r="D36" t="n">
-        <v>20484.3888888889</v>
+        <v>9187.944626450462</v>
       </c>
       <c r="E36" t="n">
-        <v>18974.94444444443</v>
+        <v>8510.907491123391</v>
       </c>
       <c r="F36" t="n">
-        <v>3035.333333333333</v>
+        <v>1361.450162890296</v>
       </c>
       <c r="G36" t="n">
-        <v>17289.27777777778</v>
+        <v>7754.828699805998</v>
       </c>
       <c r="H36" t="n">
-        <v>22017.66666666667</v>
+        <v>9875.671821808999</v>
       </c>
       <c r="I36" t="n">
-        <v>152.3888888888889</v>
+        <v>68.35159595885648</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
@@ -1792,22 +1793,22 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>69784.72222222222</v>
+        <v>31927.93864067333</v>
       </c>
       <c r="D37" t="n">
-        <v>36616.66666666663</v>
+        <v>16752.87440188498</v>
       </c>
       <c r="E37" t="n">
-        <v>33168.05555555559</v>
+        <v>15175.06423878835</v>
       </c>
       <c r="F37" t="n">
-        <v>5368.055555555556</v>
+        <v>2455.995280051794</v>
       </c>
       <c r="G37" t="n">
-        <v>68549.72222222222</v>
+        <v>31362.90086498845</v>
       </c>
       <c r="H37" t="n">
-        <v>1235</v>
+        <v>565.0377756848785</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -1829,19 +1830,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>24030.5</v>
+        <v>11760.29789312335</v>
       </c>
       <c r="D38" t="n">
-        <v>12248.88888888889</v>
+        <v>5994.489594186637</v>
       </c>
       <c r="E38" t="n">
-        <v>11781.61111111111</v>
+        <v>5765.808298936711</v>
       </c>
       <c r="F38" t="n">
-        <v>1848.5</v>
+        <v>904.6382994710268</v>
       </c>
       <c r="G38" t="n">
-        <v>24030.5</v>
+        <v>11760.29789312335</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1866,25 +1867,25 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>30887.27777777778</v>
+        <v>15055.40813319925</v>
       </c>
       <c r="D39" t="n">
-        <v>16823.44444444444</v>
+        <v>8200.263685896678</v>
       </c>
       <c r="E39" t="n">
-        <v>14063.83333333334</v>
+        <v>6855.144447302569</v>
       </c>
       <c r="F39" t="n">
-        <v>2375.944444444444</v>
+        <v>1158.108317938404</v>
       </c>
       <c r="G39" t="n">
-        <v>18109.72222222222</v>
+        <v>8827.234992867658</v>
       </c>
       <c r="H39" t="n">
-        <v>12436.66666666667</v>
+        <v>6062.013422818786</v>
       </c>
       <c r="I39" t="n">
-        <v>340.8888888888889</v>
+        <v>166.159717512803</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
@@ -1903,25 +1904,25 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39275.16666666666</v>
+        <v>17584.26779759713</v>
       </c>
       <c r="D40" t="n">
-        <v>21059.99999999999</v>
+        <v>9428.977933063614</v>
       </c>
       <c r="E40" t="n">
-        <v>18215.16666666667</v>
+        <v>8155.289864533521</v>
       </c>
       <c r="F40" t="n">
-        <v>3021.166666666667</v>
+        <v>1352.635984430549</v>
       </c>
       <c r="G40" t="n">
-        <v>30091.38888888889</v>
+        <v>13472.50910771933</v>
       </c>
       <c r="H40" t="n">
-        <v>9025.611111111109</v>
+        <v>4040.944349434019</v>
       </c>
       <c r="I40" t="n">
-        <v>158.1666666666666</v>
+        <v>70.81434044379051</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
@@ -1940,22 +1941,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>16710.05555555555</v>
+        <v>8163.647160515176</v>
       </c>
       <c r="D41" t="n">
-        <v>8764.888888888898</v>
+        <v>4282.059987898702</v>
       </c>
       <c r="E41" t="n">
-        <v>7945.166666666657</v>
+        <v>3881.587172616473</v>
       </c>
       <c r="F41" t="n">
-        <v>1285.388888888889</v>
+        <v>627.9728585011674</v>
       </c>
       <c r="G41" t="n">
-        <v>12808.61111111111</v>
+        <v>6257.608263462706</v>
       </c>
       <c r="H41" t="n">
-        <v>3901.444444444444</v>
+        <v>1906.038897052469</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -1977,22 +1978,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>77509.61111111111</v>
+        <v>35157.18964360584</v>
       </c>
       <c r="D42" t="n">
-        <v>40544.83333333334</v>
+        <v>18390.52440251571</v>
       </c>
       <c r="E42" t="n">
-        <v>36964.77777777777</v>
+        <v>16766.66524109013</v>
       </c>
       <c r="F42" t="n">
-        <v>5962.277777777777</v>
+        <v>2704.399203354295</v>
       </c>
       <c r="G42" t="n">
-        <v>59901.11111111111</v>
+        <v>27170.23983228509</v>
       </c>
       <c r="H42" t="n">
-        <v>17608.5</v>
+        <v>7986.949811320747</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2014,22 +2015,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>240552</v>
+        <v>61181.06004953831</v>
       </c>
       <c r="D43" t="n">
-        <v>127579.111111111</v>
+        <v>32447.97489921348</v>
       </c>
       <c r="E43" t="n">
-        <v>112972.888888889</v>
+        <v>28733.08515032483</v>
       </c>
       <c r="F43" t="n">
-        <v>18504</v>
+        <v>4706.235388426024</v>
       </c>
       <c r="G43" t="n">
-        <v>229080.2222222222</v>
+        <v>58263.37270918287</v>
       </c>
       <c r="H43" t="n">
-        <v>11471.77777777778</v>
+        <v>2917.687340355438</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2051,22 +2052,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>83842.05555555555</v>
+        <v>19352.72206525996</v>
       </c>
       <c r="D44" t="n">
-        <v>45274.66666666663</v>
+        <v>10450.45991288593</v>
       </c>
       <c r="E44" t="n">
-        <v>38567.38888888892</v>
+        <v>8902.262152374024</v>
       </c>
       <c r="F44" t="n">
-        <v>6449.388888888889</v>
+        <v>1488.67092809692</v>
       </c>
       <c r="G44" t="n">
-        <v>66466.11111111111</v>
+        <v>15341.94464304003</v>
       </c>
       <c r="H44" t="n">
-        <v>17375.94444444444</v>
+        <v>4010.777422219929</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2088,22 +2089,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>84846.66666666667</v>
+        <v>20514.52386424576</v>
       </c>
       <c r="D45" t="n">
-        <v>46620.16666666664</v>
+        <v>11271.98697617405</v>
       </c>
       <c r="E45" t="n">
-        <v>38226.50000000003</v>
+        <v>9242.536888071711</v>
       </c>
       <c r="F45" t="n">
-        <v>6526.666666666667</v>
+        <v>1578.040297249674</v>
       </c>
       <c r="G45" t="n">
-        <v>57080.11111111112</v>
+        <v>13801.02893332311</v>
       </c>
       <c r="H45" t="n">
-        <v>27766.55555555556</v>
+        <v>6713.494930922646</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2125,22 +2126,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>208221</v>
+        <v>53248.18469329352</v>
       </c>
       <c r="D46" t="n">
-        <v>111064.7777777777</v>
+        <v>28402.50407034213</v>
       </c>
       <c r="E46" t="n">
-        <v>97156.22222222232</v>
+        <v>24845.6806229514</v>
       </c>
       <c r="F46" t="n">
-        <v>16017</v>
+        <v>4096.014207176425</v>
       </c>
       <c r="G46" t="n">
-        <v>169274.4444444444</v>
+        <v>43288.41414474251</v>
       </c>
       <c r="H46" t="n">
-        <v>38946.55555555555</v>
+        <v>9959.770548551007</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2162,25 +2163,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>114108.2222222222</v>
+        <v>30940.91805577533</v>
       </c>
       <c r="D47" t="n">
-        <v>60843.61111111115</v>
+        <v>16497.99768100961</v>
       </c>
       <c r="E47" t="n">
-        <v>53264.61111111107</v>
+        <v>14442.92037476572</v>
       </c>
       <c r="F47" t="n">
-        <v>8777.555555555555</v>
+        <v>2380.070619675025</v>
       </c>
       <c r="G47" t="n">
-        <v>82662.66666666666</v>
+        <v>22414.32515374959</v>
       </c>
       <c r="H47" t="n">
-        <v>29861.72222222222</v>
+        <v>8097.129920074828</v>
       </c>
       <c r="I47" t="n">
-        <v>1583.833333333333</v>
+        <v>429.4629819509057</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
@@ -2199,22 +2200,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>153699.7222222222</v>
+        <v>38043.23431755223</v>
       </c>
       <c r="D48" t="n">
-        <v>82737.77777777772</v>
+        <v>20478.97433648371</v>
       </c>
       <c r="E48" t="n">
-        <v>70961.9444444445</v>
+        <v>17564.25998106852</v>
       </c>
       <c r="F48" t="n">
-        <v>11823.05555555555</v>
+        <v>2926.40263981171</v>
       </c>
       <c r="G48" t="n">
-        <v>102385.8333333333</v>
+        <v>25342.19445540865</v>
       </c>
       <c r="H48" t="n">
-        <v>51313.88888888889</v>
+        <v>12701.03986214358</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -2236,25 +2237,25 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>230383.1111111111</v>
+        <v>71803.3333333333</v>
       </c>
       <c r="D49" t="n">
-        <v>120347.5</v>
+        <v>37508.6160467974</v>
       </c>
       <c r="E49" t="n">
-        <v>110035.6111111111</v>
+        <v>34294.7172865359</v>
       </c>
       <c r="F49" t="n">
-        <v>17721.77777777778</v>
+        <v>5523.333333333331</v>
       </c>
       <c r="G49" t="n">
-        <v>214089.0555555556</v>
+        <v>66724.97712586311</v>
       </c>
       <c r="H49" t="n">
-        <v>16137.33333333333</v>
+        <v>5029.510708732505</v>
       </c>
       <c r="I49" t="n">
-        <v>156.7222222222222</v>
+        <v>48.84549873769036</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
@@ -2273,22 +2274,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>79722.5</v>
+        <v>24051.7308876951</v>
       </c>
       <c r="D50" t="n">
-        <v>40167.11111111112</v>
+        <v>12118.14164107488</v>
       </c>
       <c r="E50" t="n">
-        <v>39555.38888888888</v>
+        <v>11933.58924662022</v>
       </c>
       <c r="F50" t="n">
-        <v>6132.5</v>
+        <v>1850.133145207316</v>
       </c>
       <c r="G50" t="n">
-        <v>68503.5</v>
+        <v>20667.03561560691</v>
       </c>
       <c r="H50" t="n">
-        <v>11219</v>
+        <v>3384.695272088198</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -2310,22 +2311,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>92021.94444444445</v>
+        <v>26722.22222222219</v>
       </c>
       <c r="D51" t="n">
-        <v>51918.38888888891</v>
+        <v>15076.56389662824</v>
       </c>
       <c r="E51" t="n">
-        <v>40103.55555555555</v>
+        <v>11645.65832559395</v>
       </c>
       <c r="F51" t="n">
-        <v>7078.611111111111</v>
+        <v>2055.555555555553</v>
       </c>
       <c r="G51" t="n">
-        <v>55590.16666666666</v>
+        <v>16142.81023950606</v>
       </c>
       <c r="H51" t="n">
-        <v>36431.77777777778</v>
+        <v>10579.41198271613</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2347,25 +2348,25 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>110299.9444444445</v>
+        <v>32415.37322440984</v>
       </c>
       <c r="D52" t="n">
-        <v>59584.77777777777</v>
+        <v>17511.00437890992</v>
       </c>
       <c r="E52" t="n">
-        <v>50715.16666666669</v>
+        <v>14904.36884549992</v>
       </c>
       <c r="F52" t="n">
-        <v>8484.611111111111</v>
+        <v>2493.490248031526</v>
       </c>
       <c r="G52" t="n">
-        <v>68765.66666666667</v>
+        <v>20209.11942660214</v>
       </c>
       <c r="H52" t="n">
-        <v>39439.83333333334</v>
+        <v>11590.73038384393</v>
       </c>
       <c r="I52" t="n">
-        <v>2094.444444444445</v>
+        <v>615.523413963768</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
@@ -2384,22 +2385,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>128688.4444444445</v>
+        <v>39174.77777777784</v>
       </c>
       <c r="D53" t="n">
-        <v>71969.44444444442</v>
+        <v>21908.6259459635</v>
       </c>
       <c r="E53" t="n">
-        <v>56719.00000000003</v>
+        <v>17266.15183181434</v>
       </c>
       <c r="F53" t="n">
-        <v>9899.111111111111</v>
+        <v>3013.444444444449</v>
       </c>
       <c r="G53" t="n">
-        <v>61945.72222222223</v>
+        <v>18857.24792785987</v>
       </c>
       <c r="H53" t="n">
-        <v>66742.72222222222</v>
+        <v>20317.52984991797</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -2421,22 +2422,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>302922.3888888889</v>
+        <v>77520.81409196251</v>
       </c>
       <c r="D54" t="n">
-        <v>161828.3333333332</v>
+        <v>41413.45969560196</v>
       </c>
       <c r="E54" t="n">
-        <v>141094.0555555557</v>
+        <v>36107.35439636056</v>
       </c>
       <c r="F54" t="n">
-        <v>23301.72222222222</v>
+        <v>5963.139545535578</v>
       </c>
       <c r="G54" t="n">
-        <v>256947.1666666667</v>
+        <v>65755.30323686084</v>
       </c>
       <c r="H54" t="n">
-        <v>45975.22222222222</v>
+        <v>11765.51085510167</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2458,22 +2459,22 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>93951.72222222222</v>
+        <v>25561.80760889808</v>
       </c>
       <c r="D55" t="n">
-        <v>52008.66666666666</v>
+        <v>14150.19863269941</v>
       </c>
       <c r="E55" t="n">
-        <v>41943.05555555555</v>
+        <v>11411.60897619867</v>
       </c>
       <c r="F55" t="n">
-        <v>7227.055555555556</v>
+        <v>1966.29289299216</v>
       </c>
       <c r="G55" t="n">
-        <v>71421.27777777778</v>
+        <v>19431.86264770146</v>
       </c>
       <c r="H55" t="n">
-        <v>22530.44444444445</v>
+        <v>6129.944961196618</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -2495,22 +2496,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>121500.1666666667</v>
+        <v>31043.27777777781</v>
       </c>
       <c r="D56" t="n">
-        <v>66002.44444444444</v>
+        <v>16863.61651274473</v>
       </c>
       <c r="E56" t="n">
-        <v>55497.72222222222</v>
+        <v>14179.66126503308</v>
       </c>
       <c r="F56" t="n">
-        <v>9346.166666666666</v>
+        <v>2387.944444444447</v>
       </c>
       <c r="G56" t="n">
-        <v>108147</v>
+        <v>27631.54532161138</v>
       </c>
       <c r="H56" t="n">
-        <v>13353.16666666666</v>
+        <v>3411.732456166425</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -2532,22 +2533,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>80097.33333333333</v>
+        <v>20014.04213063562</v>
       </c>
       <c r="D57" t="n">
-        <v>43306.61111111111</v>
+        <v>10821.08858363363</v>
       </c>
       <c r="E57" t="n">
-        <v>36790.72222222222</v>
+        <v>9192.953547001993</v>
       </c>
       <c r="F57" t="n">
-        <v>6161.333333333333</v>
+        <v>1539.541702356586</v>
       </c>
       <c r="G57" t="n">
-        <v>67012.11111111111</v>
+        <v>16744.41781300184</v>
       </c>
       <c r="H57" t="n">
-        <v>13085.22222222222</v>
+        <v>3269.624317633774</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -2569,22 +2570,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>103775.3888888889</v>
+        <v>29119.39203295939</v>
       </c>
       <c r="D58" t="n">
-        <v>55052.11111111115</v>
+        <v>15447.6318792974</v>
       </c>
       <c r="E58" t="n">
-        <v>48723.27777777774</v>
+        <v>13671.76015366199</v>
       </c>
       <c r="F58" t="n">
-        <v>7982.722222222223</v>
+        <v>2239.953233304568</v>
       </c>
       <c r="G58" t="n">
-        <v>64787.66666666666</v>
+        <v>18179.4304484592</v>
       </c>
       <c r="H58" t="n">
-        <v>38987.72222222223</v>
+        <v>10939.96158450018</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2606,22 +2607,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>106326.2777777778</v>
+        <v>32033.87962528994</v>
       </c>
       <c r="D59" t="n">
-        <v>56536.99999999997</v>
+        <v>17033.41347244582</v>
       </c>
       <c r="E59" t="n">
-        <v>49789.27777777781</v>
+        <v>15000.46615284412</v>
       </c>
       <c r="F59" t="n">
-        <v>8178.944444444444</v>
+        <v>2464.144586560765</v>
       </c>
       <c r="G59" t="n">
-        <v>58680.55555555555</v>
+        <v>17679.22184711969</v>
       </c>
       <c r="H59" t="n">
-        <v>47645.72222222223</v>
+        <v>14354.65777817025</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2643,22 +2644,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>94039.83333333333</v>
+        <v>24358.76303757348</v>
       </c>
       <c r="D60" t="n">
-        <v>50772.2222222222</v>
+        <v>13151.32626424759</v>
       </c>
       <c r="E60" t="n">
-        <v>43267.61111111113</v>
+        <v>11207.43677332589</v>
       </c>
       <c r="F60" t="n">
-        <v>7233.833333333333</v>
+        <v>1873.751002890268</v>
       </c>
       <c r="G60" t="n">
-        <v>72755.22222222222</v>
+        <v>18845.49509541643</v>
       </c>
       <c r="H60" t="n">
-        <v>21284.61111111111</v>
+        <v>5513.267942157056</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
@@ -2680,25 +2681,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>107265.1666666667</v>
+        <v>30320.34873783623</v>
       </c>
       <c r="D61" t="n">
-        <v>57261.38888888889</v>
+        <v>16185.91882413494</v>
       </c>
       <c r="E61" t="n">
-        <v>50003.77777777777</v>
+        <v>14134.42991370129</v>
       </c>
       <c r="F61" t="n">
-        <v>8251.166666666666</v>
+        <v>2332.334518295094</v>
       </c>
       <c r="G61" t="n">
-        <v>8437.722222222223</v>
+        <v>2385.067662513319</v>
       </c>
       <c r="H61" t="n">
-        <v>81559.11111111111</v>
+        <v>23054.08893197844</v>
       </c>
       <c r="I61" t="n">
-        <v>17268.33333333333</v>
+        <v>4881.192143344471</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
@@ -2717,22 +2718,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>126087</v>
+        <v>43596.22222222227</v>
       </c>
       <c r="D62" t="n">
-        <v>63695.66666666673</v>
+        <v>22023.60622897363</v>
       </c>
       <c r="E62" t="n">
-        <v>62391.33333333327</v>
+        <v>21572.61599324864</v>
       </c>
       <c r="F62" t="n">
-        <v>9699</v>
+        <v>3353.555555555559</v>
       </c>
       <c r="G62" t="n">
-        <v>122808.1111111111</v>
+        <v>42462.50368944748</v>
       </c>
       <c r="H62" t="n">
-        <v>3278.888888888889</v>
+        <v>1133.718532774794</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -2754,22 +2755,22 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>94585.83333333333</v>
+        <v>31672.57517333006</v>
       </c>
       <c r="D63" t="n">
-        <v>49678.05555555558</v>
+        <v>16634.96417590585</v>
       </c>
       <c r="E63" t="n">
-        <v>44907.77777777775</v>
+        <v>15037.61099742422</v>
       </c>
       <c r="F63" t="n">
-        <v>7275.833333333333</v>
+        <v>2436.351936410005</v>
       </c>
       <c r="G63" t="n">
-        <v>82022.77777777778</v>
+        <v>27465.76843000111</v>
       </c>
       <c r="H63" t="n">
-        <v>12563.05555555556</v>
+        <v>4206.806743328954</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -2791,22 +2792,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>121183.8333333333</v>
+        <v>38343.7285180462</v>
       </c>
       <c r="D64" t="n">
-        <v>61186.66666666667</v>
+        <v>19360.04887002959</v>
       </c>
       <c r="E64" t="n">
-        <v>59997.16666666667</v>
+        <v>18983.67964801661</v>
       </c>
       <c r="F64" t="n">
-        <v>9321.833333333334</v>
+        <v>2949.517578311246</v>
       </c>
       <c r="G64" t="n">
-        <v>19519.5</v>
+        <v>6176.157233360358</v>
       </c>
       <c r="H64" t="n">
-        <v>101664.3333333333</v>
+        <v>32167.57128468584</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -2828,22 +2829,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>87945</v>
+        <v>31250.76450251286</v>
       </c>
       <c r="D65" t="n">
-        <v>42892.05555555558</v>
+        <v>15241.45235312259</v>
       </c>
       <c r="E65" t="n">
-        <v>45052.94444444442</v>
+        <v>16009.31214939028</v>
       </c>
       <c r="F65" t="n">
-        <v>6765</v>
+        <v>2403.904961731759</v>
       </c>
       <c r="G65" t="n">
-        <v>87339.77777777778</v>
+        <v>31035.70216652612</v>
       </c>
       <c r="H65" t="n">
-        <v>605.2222222222222</v>
+        <v>215.0623359867437</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -2865,22 +2866,22 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>113796.2222222222</v>
+        <v>31644.56833923574</v>
       </c>
       <c r="D66" t="n">
-        <v>58687.0555555556</v>
+        <v>16319.75564645451</v>
       </c>
       <c r="E66" t="n">
-        <v>55109.16666666662</v>
+        <v>15324.81269278122</v>
       </c>
       <c r="F66" t="n">
-        <v>8753.555555555555</v>
+        <v>2434.197564556595</v>
       </c>
       <c r="G66" t="n">
-        <v>21652.94444444445</v>
+        <v>6021.272647169573</v>
       </c>
       <c r="H66" t="n">
-        <v>92143.27777777778</v>
+        <v>25623.29569206616</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -2902,22 +2903,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>57294.61111111111</v>
+        <v>17932.50764887719</v>
       </c>
       <c r="D67" t="n">
-        <v>29398.05555555559</v>
+        <v>9201.229328352683</v>
       </c>
       <c r="E67" t="n">
-        <v>27896.55555555552</v>
+        <v>8731.278320524505</v>
       </c>
       <c r="F67" t="n">
-        <v>4407.277777777777</v>
+        <v>1379.423665298245</v>
       </c>
       <c r="G67" t="n">
-        <v>51382.5</v>
+        <v>16082.08968347011</v>
       </c>
       <c r="H67" t="n">
-        <v>5912.11111111111</v>
+        <v>1850.417965407075</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -2939,22 +2940,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>88284.44444444445</v>
+        <v>29520.10885422205</v>
       </c>
       <c r="D68" t="n">
-        <v>46790.61111111107</v>
+        <v>15645.60939413025</v>
       </c>
       <c r="E68" t="n">
-        <v>41493.83333333339</v>
+        <v>13874.4994600918</v>
       </c>
       <c r="F68" t="n">
-        <v>6791.111111111111</v>
+        <v>2270.777604170927</v>
       </c>
       <c r="G68" t="n">
-        <v>76440.00000000001</v>
+        <v>25559.62304590038</v>
       </c>
       <c r="H68" t="n">
-        <v>11844.44444444445</v>
+        <v>3960.485808321676</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -2976,25 +2977,25 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>267176.7222222222</v>
+        <v>85572.99090448202</v>
       </c>
       <c r="D69" t="n">
-        <v>137514</v>
+        <v>44043.82302980506</v>
       </c>
       <c r="E69" t="n">
-        <v>129662.7222222222</v>
+        <v>41529.16787467696</v>
       </c>
       <c r="F69" t="n">
-        <v>20552.05555555555</v>
+        <v>6582.537761883233</v>
       </c>
       <c r="G69" t="n">
-        <v>173135.4444444444</v>
+        <v>55452.87661836437</v>
       </c>
       <c r="H69" t="n">
-        <v>92213.33333333331</v>
+        <v>29534.64908534227</v>
       </c>
       <c r="I69" t="n">
-        <v>1827.944444444444</v>
+        <v>585.4652007753861</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
@@ -3013,22 +3014,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>44190.61111111111</v>
+        <v>13367.82958610723</v>
       </c>
       <c r="D70" t="n">
-        <v>22257.44444444442</v>
+        <v>6732.962429677093</v>
       </c>
       <c r="E70" t="n">
-        <v>21933.16666666669</v>
+        <v>6634.867156430137</v>
       </c>
       <c r="F70" t="n">
-        <v>3399.277777777778</v>
+        <v>1028.29458354671</v>
       </c>
       <c r="G70" t="n">
-        <v>43755.11111111111</v>
+        <v>13236.08916346153</v>
       </c>
       <c r="H70" t="n">
-        <v>435.5</v>
+        <v>131.7404226457035</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -3050,22 +3051,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>79900.88888888889</v>
+        <v>24869.9470210781</v>
       </c>
       <c r="D71" t="n">
-        <v>41153.66666666664</v>
+        <v>12809.4884043954</v>
       </c>
       <c r="E71" t="n">
-        <v>38747.22222222226</v>
+        <v>12060.45861668271</v>
       </c>
       <c r="F71" t="n">
-        <v>6146.222222222223</v>
+        <v>1913.072847775239</v>
       </c>
       <c r="G71" t="n">
-        <v>57794.38888888889</v>
+        <v>17989.07884217706</v>
       </c>
       <c r="H71" t="n">
-        <v>22106.5</v>
+        <v>6880.868178901038</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -3087,22 +3088,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>89865.38888888889</v>
+        <v>32664.99452101888</v>
       </c>
       <c r="D72" t="n">
-        <v>44842.05555555553</v>
+        <v>16299.5511079856</v>
       </c>
       <c r="E72" t="n">
-        <v>45023.33333333336</v>
+        <v>16365.44341303328</v>
       </c>
       <c r="F72" t="n">
-        <v>6912.722222222223</v>
+        <v>2512.691886232222</v>
       </c>
       <c r="G72" t="n">
-        <v>75819.61111111111</v>
+        <v>27559.52221597122</v>
       </c>
       <c r="H72" t="n">
-        <v>14045.77777777778</v>
+        <v>5105.47230504766</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -3124,19 +3125,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>40190.22222222223</v>
+        <v>13149.5</v>
       </c>
       <c r="D73" t="n">
-        <v>20401.33333333335</v>
+        <v>6674.940267395057</v>
       </c>
       <c r="E73" t="n">
-        <v>19788.88888888888</v>
+        <v>6474.559732604939</v>
       </c>
       <c r="F73" t="n">
-        <v>3091.555555555556</v>
+        <v>1011.5</v>
       </c>
       <c r="G73" t="n">
-        <v>40190.22222222223</v>
+        <v>13149.5</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3161,22 +3162,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>88306.83333333333</v>
+        <v>32792.04596930291</v>
       </c>
       <c r="D74" t="n">
-        <v>45832.94444444445</v>
+        <v>17019.70237634379</v>
       </c>
       <c r="E74" t="n">
-        <v>42473.88888888888</v>
+        <v>15772.34359295912</v>
       </c>
       <c r="F74" t="n">
-        <v>6792.833333333333</v>
+        <v>2522.465074561762</v>
       </c>
       <c r="G74" t="n">
-        <v>87700.16666666666</v>
+        <v>32566.7650881928</v>
       </c>
       <c r="H74" t="n">
-        <v>606.6666666666666</v>
+        <v>225.2808811101115</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -3198,19 +3199,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>37296.27777777777</v>
+        <v>11984.34949602523</v>
       </c>
       <c r="D75" t="n">
-        <v>15925.72222222224</v>
+        <v>5117.385231441153</v>
       </c>
       <c r="E75" t="n">
-        <v>21370.55555555553</v>
+        <v>6866.964264584073</v>
       </c>
       <c r="F75" t="n">
-        <v>2868.944444444444</v>
+        <v>921.8730381557866</v>
       </c>
       <c r="G75" t="n">
-        <v>37296.27777777777</v>
+        <v>11984.34949602523</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3235,22 +3236,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>201920.3333333333</v>
+        <v>73367.66666666658</v>
       </c>
       <c r="D76" t="n">
-        <v>96290.27777777775</v>
+        <v>34987.03120491777</v>
       </c>
       <c r="E76" t="n">
-        <v>105630.0555555556</v>
+        <v>38380.63546174882</v>
       </c>
       <c r="F76" t="n">
-        <v>15532.33333333333</v>
+        <v>5643.666666666661</v>
       </c>
       <c r="G76" t="n">
-        <v>188175.7222222222</v>
+        <v>68373.5681040505</v>
       </c>
       <c r="H76" t="n">
-        <v>13744.61111111111</v>
+        <v>4994.09856261609</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -3272,25 +3273,25 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>115093.3333333333</v>
+        <v>34103.25311512306</v>
       </c>
       <c r="D77" t="n">
-        <v>60156.05555555557</v>
+        <v>17824.81338929433</v>
       </c>
       <c r="E77" t="n">
-        <v>54937.27777777777</v>
+        <v>16278.43972582872</v>
       </c>
       <c r="F77" t="n">
-        <v>8853.333333333334</v>
+        <v>2623.327162701774</v>
       </c>
       <c r="G77" t="n">
-        <v>87393.94444444445</v>
+        <v>25895.65982493534</v>
       </c>
       <c r="H77" t="n">
-        <v>18954.72222222223</v>
+        <v>5616.465097931757</v>
       </c>
       <c r="I77" t="n">
-        <v>8744.666666666668</v>
+        <v>2591.128192255961</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
@@ -3309,25 +3310,25 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>92248.72222222222</v>
+        <v>31766.24610102878</v>
       </c>
       <c r="D78" t="n">
-        <v>49294.55555555552</v>
+        <v>16974.7932057686</v>
       </c>
       <c r="E78" t="n">
-        <v>42954.1666666667</v>
+        <v>14791.45289526019</v>
       </c>
       <c r="F78" t="n">
-        <v>7096.055555555556</v>
+        <v>2443.55739238683</v>
       </c>
       <c r="G78" t="n">
-        <v>30791.94444444444</v>
+        <v>10603.33912046099</v>
       </c>
       <c r="H78" t="n">
-        <v>44941.72222222222</v>
+        <v>15475.87623898033</v>
       </c>
       <c r="I78" t="n">
-        <v>16515.05555555555</v>
+        <v>5687.030741587464</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="n">
@@ -3346,25 +3347,25 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>82329.72222222222</v>
+        <v>28418.02565335972</v>
       </c>
       <c r="D79" t="n">
-        <v>43393.27777777781</v>
+        <v>14978.20286267655</v>
       </c>
       <c r="E79" t="n">
-        <v>38936.44444444441</v>
+        <v>13439.82279068317</v>
       </c>
       <c r="F79" t="n">
-        <v>6333.055555555556</v>
+        <v>2186.001973335363</v>
       </c>
       <c r="G79" t="n">
-        <v>43744.27777777778</v>
+        <v>15099.35870694631</v>
       </c>
       <c r="H79" t="n">
-        <v>23402.88888888889</v>
+        <v>8078.053452094112</v>
       </c>
       <c r="I79" t="n">
-        <v>15182.55555555555</v>
+        <v>5240.613494319295</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
@@ -3383,25 +3384,25 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>95924.11111111111</v>
+        <v>33143.00092606532</v>
       </c>
       <c r="D80" t="n">
-        <v>47252.11111111109</v>
+        <v>16326.20562415296</v>
       </c>
       <c r="E80" t="n">
-        <v>48672.00000000002</v>
+        <v>16816.79530191235</v>
       </c>
       <c r="F80" t="n">
-        <v>7378.777777777777</v>
+        <v>2549.461609697332</v>
       </c>
       <c r="G80" t="n">
-        <v>59997.88888888889</v>
+        <v>20730.03402349042</v>
       </c>
       <c r="H80" t="n">
-        <v>10111.11111111111</v>
+        <v>3493.517542538771</v>
       </c>
       <c r="I80" t="n">
-        <v>25815.11111111111</v>
+        <v>8919.449360036129</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
@@ -3420,25 +3421,25 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>223280.0555555556</v>
+        <v>73687.85663148512</v>
       </c>
       <c r="D81" t="n">
-        <v>114331.3888888888</v>
+        <v>37732.14303427464</v>
       </c>
       <c r="E81" t="n">
-        <v>108948.6666666667</v>
+        <v>35955.71359721048</v>
       </c>
       <c r="F81" t="n">
-        <v>17175.38888888889</v>
+        <v>5668.296663960394</v>
       </c>
       <c r="G81" t="n">
-        <v>217876.3888888889</v>
+        <v>71904.51501762299</v>
       </c>
       <c r="H81" t="n">
-        <v>5174</v>
+        <v>1707.54602000912</v>
       </c>
       <c r="I81" t="n">
-        <v>229.6666666666667</v>
+        <v>75.79559385300112</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
@@ -3457,22 +3458,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>133244.9444444444</v>
+        <v>52669.78548392336</v>
       </c>
       <c r="D82" t="n">
-        <v>65141.5555555555</v>
+        <v>25749.50795698453</v>
       </c>
       <c r="E82" t="n">
-        <v>68103.38888888893</v>
+        <v>26920.27752693882</v>
       </c>
       <c r="F82" t="n">
-        <v>10249.61111111111</v>
+        <v>4051.521960301797</v>
       </c>
       <c r="G82" t="n">
-        <v>131380.1666666667</v>
+        <v>51932.66599364735</v>
       </c>
       <c r="H82" t="n">
-        <v>1864.777777777778</v>
+        <v>737.1194902760002</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -3494,25 +3495,25 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>101577.6666666667</v>
+        <v>38338.17185815077</v>
       </c>
       <c r="D83" t="n">
-        <v>52184.88888888888</v>
+        <v>19695.9952347208</v>
       </c>
       <c r="E83" t="n">
-        <v>49392.7777777778</v>
+        <v>18642.17662342998</v>
       </c>
       <c r="F83" t="n">
-        <v>7813.666666666667</v>
+        <v>2949.090142934675</v>
       </c>
       <c r="G83" t="n">
-        <v>55536.72222222223</v>
+        <v>20961.0682235984</v>
       </c>
       <c r="H83" t="n">
-        <v>44166.05555555556</v>
+        <v>16669.46961621016</v>
       </c>
       <c r="I83" t="n">
-        <v>1874.888888888889</v>
+        <v>707.6340183422167</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
@@ -3531,25 +3532,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>83668.72222222222</v>
+        <v>31627.81115973468</v>
       </c>
       <c r="D84" t="n">
-        <v>40852.49999999996</v>
+        <v>15442.74994389585</v>
       </c>
       <c r="E84" t="n">
-        <v>42816.22222222226</v>
+        <v>16185.06121583883</v>
       </c>
       <c r="F84" t="n">
-        <v>6436.055555555556</v>
+        <v>2432.908550748822</v>
       </c>
       <c r="G84" t="n">
-        <v>29513.61111111111</v>
+        <v>11156.50979328745</v>
       </c>
       <c r="H84" t="n">
-        <v>46474.99999999999</v>
+        <v>17568.1244389587</v>
       </c>
       <c r="I84" t="n">
-        <v>7680.11111111111</v>
+        <v>2903.176927488529</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
@@ -3568,19 +3569,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>109473</v>
+        <v>36625.57496190057</v>
       </c>
       <c r="D85" t="n">
-        <v>53083.33333333334</v>
+        <v>17759.69969058631</v>
       </c>
       <c r="E85" t="n">
-        <v>56389.66666666666</v>
+        <v>18865.87527131426</v>
       </c>
       <c r="F85" t="n">
-        <v>8421</v>
+        <v>2817.351920146198</v>
       </c>
       <c r="G85" t="n">
-        <v>109473</v>
+        <v>36625.57496190057</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3605,22 +3606,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>63837.22222222223</v>
+        <v>24178.73068578352</v>
       </c>
       <c r="D86" t="n">
-        <v>29639.27777777778</v>
+        <v>11226.05417596866</v>
       </c>
       <c r="E86" t="n">
-        <v>34197.94444444445</v>
+        <v>12952.67650981486</v>
       </c>
       <c r="F86" t="n">
-        <v>4910.555555555556</v>
+        <v>1859.902360444886</v>
       </c>
       <c r="G86" t="n">
-        <v>63121.5</v>
+        <v>23907.64660263371</v>
       </c>
       <c r="H86" t="n">
-        <v>715.7222222222222</v>
+        <v>271.0840831498073</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -3642,19 +3643,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>371039.5</v>
+        <v>103046.7871523115</v>
       </c>
       <c r="D87" t="n">
-        <v>193034.1111111111</v>
+        <v>53610.31631619361</v>
       </c>
       <c r="E87" t="n">
-        <v>178005.3888888889</v>
+        <v>49436.47083611792</v>
       </c>
       <c r="F87" t="n">
-        <v>28541.5</v>
+        <v>7926.675934793195</v>
       </c>
       <c r="G87" t="n">
-        <v>371039.5</v>
+        <v>103046.7871523115</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3679,19 +3680,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>132875.8888888889</v>
+        <v>43883.17629764906</v>
       </c>
       <c r="D88" t="n">
-        <v>69827.33333333333</v>
+        <v>23060.95714342653</v>
       </c>
       <c r="E88" t="n">
-        <v>63048.55555555558</v>
+        <v>20822.21915422252</v>
       </c>
       <c r="F88" t="n">
-        <v>10221.22222222222</v>
+        <v>3375.628945973005</v>
       </c>
       <c r="G88" t="n">
-        <v>132875.8888888889</v>
+        <v>43883.17629764906</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -3716,22 +3717,22 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>157027</v>
+        <v>45323.66616228054</v>
       </c>
       <c r="D89" t="n">
-        <v>82643.16666666658</v>
+        <v>23853.80410116545</v>
       </c>
       <c r="E89" t="n">
-        <v>74383.83333333342</v>
+        <v>21469.86206111509</v>
       </c>
       <c r="F89" t="n">
-        <v>12079</v>
+        <v>3486.435858636964</v>
       </c>
       <c r="G89" t="n">
-        <v>140587.0555555556</v>
+        <v>40578.50416003609</v>
       </c>
       <c r="H89" t="n">
-        <v>16439.94444444445</v>
+        <v>4745.162002244446</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -3753,22 +3754,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>191981.8333333333</v>
+        <v>60873.22222222226</v>
       </c>
       <c r="D90" t="n">
-        <v>100093.5</v>
+        <v>31737.45016759401</v>
       </c>
       <c r="E90" t="n">
-        <v>91888.33333333331</v>
+        <v>29135.77205462825</v>
       </c>
       <c r="F90" t="n">
-        <v>14767.83333333333</v>
+        <v>4682.555555555558</v>
       </c>
       <c r="G90" t="n">
-        <v>184550.1666666667</v>
+        <v>58516.80396833462</v>
       </c>
       <c r="H90" t="n">
-        <v>7431.666666666667</v>
+        <v>2356.418253887643</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -3790,25 +3791,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>78522.88888888889</v>
+        <v>25679.31967554058</v>
       </c>
       <c r="D91" t="n">
-        <v>39538.05555555556</v>
+        <v>12930.11989659568</v>
       </c>
       <c r="E91" t="n">
-        <v>38984.83333333333</v>
+        <v>12749.1997789449</v>
       </c>
       <c r="F91" t="n">
-        <v>6040.222222222223</v>
+        <v>1975.332282733891</v>
       </c>
       <c r="G91" t="n">
-        <v>56651.11111111111</v>
+        <v>18526.59794846955</v>
       </c>
       <c r="H91" t="n">
-        <v>19515.88888888889</v>
+        <v>6382.276004124734</v>
       </c>
       <c r="I91" t="n">
-        <v>2355.888888888889</v>
+        <v>770.4457229462986</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
@@ -3827,25 +3828,25 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>222795.4444444444</v>
+        <v>60834.61662985587</v>
       </c>
       <c r="D92" t="n">
-        <v>116096.5</v>
+        <v>31700.3163470391</v>
       </c>
       <c r="E92" t="n">
-        <v>106698.9444444444</v>
+        <v>29134.30028281677</v>
       </c>
       <c r="F92" t="n">
-        <v>17138.11111111111</v>
+        <v>4679.585894604298</v>
       </c>
       <c r="G92" t="n">
-        <v>174798.7222222222</v>
+        <v>47729.04257667248</v>
       </c>
       <c r="H92" t="n">
-        <v>47878.27777777778</v>
+        <v>13073.23262722793</v>
       </c>
       <c r="I92" t="n">
-        <v>118.4444444444444</v>
+        <v>32.34142595546107</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="n">
@@ -3864,22 +3865,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>160633.0555555556</v>
+        <v>46133.39638687055</v>
       </c>
       <c r="D93" t="n">
-        <v>82823.72222222223</v>
+        <v>23786.75792662334</v>
       </c>
       <c r="E93" t="n">
-        <v>77809.33333333333</v>
+        <v>22346.63846024722</v>
       </c>
       <c r="F93" t="n">
-        <v>12356.38888888889</v>
+        <v>3548.722798990043</v>
       </c>
       <c r="G93" t="n">
-        <v>158498.8888888889</v>
+        <v>45520.46926269637</v>
       </c>
       <c r="H93" t="n">
-        <v>2134.166666666667</v>
+        <v>612.9271241741901</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -3901,25 +3902,25 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>78012.27777777778</v>
+        <v>27333.98137998573</v>
       </c>
       <c r="D94" t="n">
-        <v>40707.33333333334</v>
+        <v>14263.05606063412</v>
       </c>
       <c r="E94" t="n">
-        <v>37304.94444444445</v>
+        <v>13070.92531935161</v>
       </c>
       <c r="F94" t="n">
-        <v>6000.944444444444</v>
+        <v>2102.613952306595</v>
       </c>
       <c r="G94" t="n">
-        <v>29595.22222222222</v>
+        <v>10369.58894423151</v>
       </c>
       <c r="H94" t="n">
-        <v>48387.44444444445</v>
+        <v>16954.01727965306</v>
       </c>
       <c r="I94" t="n">
-        <v>29.61111111111111</v>
+        <v>10.37515610116385</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
@@ -3938,22 +3939,22 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>197555.2222222222</v>
+        <v>59508.79645782608</v>
       </c>
       <c r="D95" t="n">
-        <v>104646.3888888889</v>
+        <v>31522.22748852705</v>
       </c>
       <c r="E95" t="n">
-        <v>92908.8333333333</v>
+        <v>27986.56896929903</v>
       </c>
       <c r="F95" t="n">
-        <v>15196.55555555555</v>
+        <v>4577.599727525083</v>
       </c>
       <c r="G95" t="n">
-        <v>182812.5</v>
+        <v>55067.90319219716</v>
       </c>
       <c r="H95" t="n">
-        <v>14742.72222222222</v>
+        <v>4440.893265628922</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -3975,22 +3976,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>120959.2222222222</v>
+        <v>36127.2157080504</v>
       </c>
       <c r="D96" t="n">
-        <v>63902.2222222222</v>
+        <v>19085.84830518085</v>
       </c>
       <c r="E96" t="n">
-        <v>57057.00000000001</v>
+        <v>17041.36740286956</v>
       </c>
       <c r="F96" t="n">
-        <v>9304.555555555555</v>
+        <v>2779.016592926954</v>
       </c>
       <c r="G96" t="n">
-        <v>120497</v>
+        <v>35989.16255575253</v>
       </c>
       <c r="H96" t="n">
-        <v>462.2222222222222</v>
+        <v>138.0531522978724</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4012,25 +4013,25 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>73493.33333333333</v>
+        <v>23054.05555555555</v>
       </c>
       <c r="D97" t="n">
-        <v>38895.2777777778</v>
+        <v>12201.02360401381</v>
       </c>
       <c r="E97" t="n">
-        <v>34598.05555555553</v>
+        <v>10853.03195154175</v>
       </c>
       <c r="F97" t="n">
-        <v>5653.333333333333</v>
+        <v>1773.388888888889</v>
       </c>
       <c r="G97" t="n">
-        <v>39829.83333333334</v>
+        <v>12494.18346927411</v>
       </c>
       <c r="H97" t="n">
-        <v>33657.72222222222</v>
+        <v>10558.05966053022</v>
       </c>
       <c r="I97" t="n">
-        <v>5.777777777777777</v>
+        <v>1.812425751222921</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="n">
@@ -4049,22 +4050,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>91548.88888888889</v>
+        <v>24262.71614677838</v>
       </c>
       <c r="D98" t="n">
-        <v>46778.33333333336</v>
+        <v>12397.41341769357</v>
       </c>
       <c r="E98" t="n">
-        <v>44770.55555555553</v>
+        <v>11865.30272908481</v>
       </c>
       <c r="F98" t="n">
-        <v>7042.222222222223</v>
+        <v>1866.362780521414</v>
       </c>
       <c r="G98" t="n">
-        <v>91491.11111111111</v>
+        <v>24247.40360897669</v>
       </c>
       <c r="H98" t="n">
-        <v>57.77777777777778</v>
+        <v>15.31253780169036</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4086,22 +4087,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>105813.5</v>
+        <v>25969.29894750498</v>
       </c>
       <c r="D99" t="n">
-        <v>54957.49999999996</v>
+        <v>13487.95519387889</v>
       </c>
       <c r="E99" t="n">
-        <v>50856.00000000004</v>
+        <v>12481.34375362609</v>
       </c>
       <c r="F99" t="n">
-        <v>8139.5</v>
+        <v>1997.638380577306</v>
       </c>
       <c r="G99" t="n">
-        <v>105647.3888888889</v>
+        <v>25928.53109554898</v>
       </c>
       <c r="H99" t="n">
-        <v>166.1111111111111</v>
+        <v>40.7678519560043</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4123,22 +4124,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>101090.8888888889</v>
+        <v>23872.12275892838</v>
       </c>
       <c r="D100" t="n">
-        <v>52547.44444444439</v>
+        <v>12408.82396260759</v>
       </c>
       <c r="E100" t="n">
-        <v>48543.4444444445</v>
+        <v>11463.29879632079</v>
       </c>
       <c r="F100" t="n">
-        <v>7776.222222222223</v>
+        <v>1836.317135302183</v>
       </c>
       <c r="G100" t="n">
-        <v>100895.8888888889</v>
+        <v>23826.07445537545</v>
       </c>
       <c r="H100" t="n">
-        <v>195</v>
+        <v>46.0483035529296</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
@@ -4160,19 +4161,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>110722.4444444445</v>
+        <v>33950.22222222226</v>
       </c>
       <c r="D101" t="n">
-        <v>57528.6111111111</v>
+        <v>17639.68580316169</v>
       </c>
       <c r="E101" t="n">
-        <v>53193.83333333335</v>
+        <v>16310.53641906056</v>
       </c>
       <c r="F101" t="n">
-        <v>8517.111111111111</v>
+        <v>2611.555555555558</v>
       </c>
       <c r="G101" t="n">
-        <v>110722.4444444445</v>
+        <v>33950.22222222226</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -4197,22 +4198,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>129992.0555555555</v>
+        <v>41247.78472391982</v>
       </c>
       <c r="D102" t="n">
-        <v>68228.33333333333</v>
+        <v>21649.53537643248</v>
       </c>
       <c r="E102" t="n">
-        <v>61763.72222222222</v>
+        <v>19598.24934748734</v>
       </c>
       <c r="F102" t="n">
-        <v>9999.388888888889</v>
+        <v>3172.906517224601</v>
       </c>
       <c r="G102" t="n">
-        <v>127218.7222222222</v>
+        <v>40367.7782049667</v>
       </c>
       <c r="H102" t="n">
-        <v>2773.333333333333</v>
+        <v>880.0065189531143</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -4234,22 +4235,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>89895.72222222222</v>
+        <v>25561.61111111112</v>
       </c>
       <c r="D103" t="n">
-        <v>47066.50000000003</v>
+        <v>13383.23492620772</v>
       </c>
       <c r="E103" t="n">
-        <v>42829.22222222219</v>
+        <v>12178.37618490339</v>
       </c>
       <c r="F103" t="n">
-        <v>6915.055555555556</v>
+        <v>1966.277777777778</v>
       </c>
       <c r="G103" t="n">
-        <v>86592.27777777778</v>
+        <v>24622.28541097034</v>
       </c>
       <c r="H103" t="n">
-        <v>3303.444444444444</v>
+        <v>939.3257001407736</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -4271,22 +4272,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>92620.66666666667</v>
+        <v>25924.71612138604</v>
       </c>
       <c r="D104" t="n">
-        <v>48296.44444444445</v>
+        <v>13518.27466758154</v>
       </c>
       <c r="E104" t="n">
-        <v>44324.22222222222</v>
+        <v>12406.4414538045</v>
       </c>
       <c r="F104" t="n">
-        <v>7124.666666666667</v>
+        <v>1994.208932414311</v>
       </c>
       <c r="G104" t="n">
-        <v>89516.55555555556</v>
+        <v>25055.86900269263</v>
       </c>
       <c r="H104" t="n">
-        <v>3104.111111111111</v>
+        <v>868.8471186934062</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -4308,22 +4309,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>509.1666666666666</v>
+        <v>121.0916382468107</v>
       </c>
       <c r="D105" t="n">
-        <v>267.2017502951166</v>
+        <v>63.5467712320476</v>
       </c>
       <c r="E105" t="n">
-        <v>241.96491637155</v>
+        <v>57.5448670147631</v>
       </c>
       <c r="F105" t="n">
-        <v>39.16666666666666</v>
+        <v>9.314741403600824</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>509.1666666666666</v>
+        <v>121.0916382468107</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -4345,22 +4346,22 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>126068.2222222222</v>
+        <v>30393.97426427528</v>
       </c>
       <c r="D106" t="n">
-        <v>66019.05555555556</v>
+        <v>15916.6318056765</v>
       </c>
       <c r="E106" t="n">
-        <v>60049.16666666666</v>
+        <v>14477.34245859877</v>
       </c>
       <c r="F106" t="n">
-        <v>9697.555555555555</v>
+        <v>2337.998020328867</v>
       </c>
       <c r="G106" t="n">
-        <v>124777.6111111111</v>
+        <v>30082.81892151845</v>
       </c>
       <c r="H106" t="n">
-        <v>1290.611111111111</v>
+        <v>311.1553427568225</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -4382,22 +4383,22 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>86333</v>
+        <v>21013.58292550302</v>
       </c>
       <c r="D107" t="n">
-        <v>45436.44444444442</v>
+        <v>11059.29937768112</v>
       </c>
       <c r="E107" t="n">
-        <v>40896.55555555558</v>
+        <v>9954.283547821902</v>
       </c>
       <c r="F107" t="n">
-        <v>6641</v>
+        <v>1616.429455807925</v>
       </c>
       <c r="G107" t="n">
-        <v>76006.66666666667</v>
+        <v>18500.13775602685</v>
       </c>
       <c r="H107" t="n">
-        <v>10326.33333333333</v>
+        <v>2513.445169476168</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -4419,22 +4420,22 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>100245.1666666667</v>
+        <v>28724.73749537714</v>
       </c>
       <c r="D108" t="n">
-        <v>55301.2777777778</v>
+        <v>15846.29703502513</v>
       </c>
       <c r="E108" t="n">
-        <v>44943.88888888888</v>
+        <v>12878.44046035201</v>
       </c>
       <c r="F108" t="n">
-        <v>7711.166666666667</v>
+        <v>2209.595191952088</v>
       </c>
       <c r="G108" t="n">
-        <v>99265.83333333334</v>
+        <v>28444.11456006881</v>
       </c>
       <c r="H108" t="n">
-        <v>979.3333333333334</v>
+        <v>280.6229353083292</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -4456,22 +4457,22 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1349.111111111111</v>
+        <v>376.8618737976473</v>
       </c>
       <c r="D109" t="n">
-        <v>748.5486601484702</v>
+        <v>209.100235235582</v>
       </c>
       <c r="E109" t="n">
-        <v>600.5624509626409</v>
+        <v>167.7616385620653</v>
       </c>
       <c r="F109" t="n">
-        <v>103.7777777777778</v>
+        <v>28.98937490751133</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>1349.111111111111</v>
+        <v>376.8618737976473</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -4493,19 +4494,19 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>119037.3888888889</v>
+        <v>38152.60185432366</v>
       </c>
       <c r="D110" t="n">
-        <v>63606.83333333337</v>
+        <v>20386.58786145055</v>
       </c>
       <c r="E110" t="n">
-        <v>55430.55555555552</v>
+        <v>17766.01399287311</v>
       </c>
       <c r="F110" t="n">
-        <v>9156.722222222223</v>
+        <v>2934.815527255666</v>
       </c>
       <c r="G110" t="n">
-        <v>119037.3888888889</v>
+        <v>38152.60185432366</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -4530,22 +4531,22 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>154543.2777777778</v>
+        <v>46434.77255771251</v>
       </c>
       <c r="D111" t="n">
-        <v>85235.22222222216</v>
+        <v>25610.16056283028</v>
       </c>
       <c r="E111" t="n">
-        <v>69308.05555555562</v>
+        <v>20824.61199488223</v>
       </c>
       <c r="F111" t="n">
-        <v>11887.94444444445</v>
+        <v>3571.905581362501</v>
       </c>
       <c r="G111" t="n">
-        <v>152583.1666666667</v>
+        <v>45845.8287036604</v>
       </c>
       <c r="H111" t="n">
-        <v>1960.111111111111</v>
+        <v>588.9438540521057</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -4567,22 +4568,22 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>122127.7777777778</v>
+        <v>34508.50000000002</v>
       </c>
       <c r="D112" t="n">
-        <v>64707.49999999996</v>
+        <v>18283.7909964518</v>
       </c>
       <c r="E112" t="n">
-        <v>57420.27777777782</v>
+        <v>16224.70900354822</v>
       </c>
       <c r="F112" t="n">
-        <v>9394.444444444445</v>
+        <v>2654.500000000002</v>
       </c>
       <c r="G112" t="n">
-        <v>120950.5555555556</v>
+        <v>34175.86336487288</v>
       </c>
       <c r="H112" t="n">
-        <v>1177.222222222222</v>
+        <v>332.6366351271439</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -4604,22 +4605,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>38905.38888888889</v>
+        <v>11917.16766392343</v>
       </c>
       <c r="D113" t="n">
-        <v>20137.72222222224</v>
+        <v>6168.415711692761</v>
       </c>
       <c r="E113" t="n">
-        <v>18767.66666666665</v>
+        <v>5748.751952230671</v>
       </c>
       <c r="F113" t="n">
-        <v>2992.722222222222</v>
+        <v>916.7052049171871</v>
       </c>
       <c r="G113" t="n">
-        <v>38614.33333333334</v>
+        <v>11828.01400284635</v>
       </c>
       <c r="H113" t="n">
-        <v>291.0555555555556</v>
+        <v>89.15366107707852</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -4641,22 +4642,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>176121.1111111111</v>
+        <v>49965.90979176414</v>
       </c>
       <c r="D114" t="n">
-        <v>94780.11111111104</v>
+        <v>26889.30618228644</v>
       </c>
       <c r="E114" t="n">
-        <v>81341.00000000006</v>
+        <v>23076.6036094777</v>
       </c>
       <c r="F114" t="n">
-        <v>13547.77777777778</v>
+        <v>3843.531522443395</v>
       </c>
       <c r="G114" t="n">
-        <v>174174.7222222222</v>
+        <v>49413.71538969409</v>
       </c>
       <c r="H114" t="n">
-        <v>1946.388888888889</v>
+        <v>552.194402070058</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -4678,22 +4679,22 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>35475.55555555555</v>
+        <v>10364.91130925724</v>
       </c>
       <c r="D115" t="n">
-        <v>17984.05555555554</v>
+        <v>5254.410759605338</v>
       </c>
       <c r="E115" t="n">
-        <v>17491.50000000001</v>
+        <v>5110.500549651899</v>
       </c>
       <c r="F115" t="n">
-        <v>2728.888888888889</v>
+        <v>797.3008699428643</v>
       </c>
       <c r="G115" t="n">
-        <v>34127.88888888889</v>
+        <v>9971.162846246772</v>
       </c>
       <c r="H115" t="n">
-        <v>1347.666666666667</v>
+        <v>393.7484630104642</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -4715,22 +4716,22 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>44324.22222222223</v>
+        <v>10067.94182558177</v>
       </c>
       <c r="D116" t="n">
-        <v>23501.11111111111</v>
+        <v>5338.115541361379</v>
       </c>
       <c r="E116" t="n">
-        <v>20823.11111111112</v>
+        <v>4729.826284220387</v>
       </c>
       <c r="F116" t="n">
-        <v>3409.555555555556</v>
+        <v>774.4570635062896</v>
       </c>
       <c r="G116" t="n">
-        <v>43886.55555555555</v>
+        <v>9968.528856372637</v>
       </c>
       <c r="H116" t="n">
-        <v>437.6666666666667</v>
+        <v>99.41296920912713</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -4752,22 +4753,22 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>56108</v>
+        <v>13002.16666666665</v>
       </c>
       <c r="D117" t="n">
-        <v>29330.16666666668</v>
+        <v>6796.815344712174</v>
       </c>
       <c r="E117" t="n">
-        <v>26777.83333333332</v>
+        <v>6205.351321954472</v>
       </c>
       <c r="F117" t="n">
-        <v>4316</v>
+        <v>1000.166666666665</v>
       </c>
       <c r="G117" t="n">
-        <v>55559.83333333334</v>
+        <v>12875.13746653278</v>
       </c>
       <c r="H117" t="n">
-        <v>548.1666666666666</v>
+        <v>127.0292001338686</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -4789,22 +4790,22 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>175445.8333333333</v>
+        <v>47697.39269233461</v>
       </c>
       <c r="D118" t="n">
-        <v>91788.66666666667</v>
+        <v>24954.02709500541</v>
       </c>
       <c r="E118" t="n">
-        <v>83657.16666666667</v>
+        <v>22743.36559732919</v>
       </c>
       <c r="F118" t="n">
-        <v>13495.83333333333</v>
+        <v>3669.030207102662</v>
       </c>
       <c r="G118" t="n">
-        <v>175185.8333333333</v>
+        <v>47626.70807210515</v>
       </c>
       <c r="H118" t="n">
-        <v>260</v>
+        <v>70.68462022945542</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -4826,25 +4827,25 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>217627.2222222222</v>
+        <v>60729.7854734183</v>
       </c>
       <c r="D119" t="n">
-        <v>119527.7777777777</v>
+        <v>33354.72570222255</v>
       </c>
       <c r="E119" t="n">
-        <v>98099.44444444453</v>
+        <v>27375.05977119575</v>
       </c>
       <c r="F119" t="n">
-        <v>16740.55555555555</v>
+        <v>4671.521959493715</v>
       </c>
       <c r="G119" t="n">
-        <v>181451.1111111111</v>
+        <v>50634.69054638308</v>
       </c>
       <c r="H119" t="n">
-        <v>34686.16666666666</v>
+        <v>9679.31970574407</v>
       </c>
       <c r="I119" t="n">
-        <v>1489.944444444444</v>
+        <v>415.7752212911491</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="n">
@@ -4863,22 +4864,22 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>160472.7222222222</v>
+        <v>46226.34750963379</v>
       </c>
       <c r="D120" t="n">
-        <v>90189.66666666663</v>
+        <v>25980.3586265456</v>
       </c>
       <c r="E120" t="n">
-        <v>70283.05555555559</v>
+        <v>20245.98888308819</v>
       </c>
       <c r="F120" t="n">
-        <v>12344.05555555555</v>
+        <v>3555.872885356445</v>
       </c>
       <c r="G120" t="n">
-        <v>136410.4444444444</v>
+        <v>39294.88153195461</v>
       </c>
       <c r="H120" t="n">
-        <v>24062.27777777778</v>
+        <v>6931.465977679175</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -4900,25 +4901,25 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>174220.9444444444</v>
+        <v>51627.11931628182</v>
       </c>
       <c r="D121" t="n">
-        <v>96159.55555555549</v>
+        <v>28495.08630490953</v>
       </c>
       <c r="E121" t="n">
-        <v>78061.38888888895</v>
+        <v>23132.03301137228</v>
       </c>
       <c r="F121" t="n">
-        <v>13401.61111111111</v>
+        <v>3971.316870483216</v>
       </c>
       <c r="G121" t="n">
-        <v>142103.7222222222</v>
+        <v>42109.78103607897</v>
       </c>
       <c r="H121" t="n">
-        <v>31577.72222222222</v>
+        <v>9357.467542732382</v>
       </c>
       <c r="I121" t="n">
-        <v>539.5</v>
+        <v>159.8707374704638</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="n">
@@ -4937,22 +4938,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>127722.1111111111</v>
+        <v>42318.13252372413</v>
       </c>
       <c r="D122" t="n">
-        <v>68675.38888888891</v>
+        <v>22754.19802284702</v>
       </c>
       <c r="E122" t="n">
-        <v>59046.7222222222</v>
+        <v>19563.9345008771</v>
       </c>
       <c r="F122" t="n">
-        <v>9824.777777777777</v>
+        <v>3255.240963363394</v>
       </c>
       <c r="G122" t="n">
-        <v>109837.7222222222</v>
+        <v>36392.50279116031</v>
       </c>
       <c r="H122" t="n">
-        <v>17884.38888888889</v>
+        <v>5925.629732563816</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -4974,22 +4975,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>77147.05555555555</v>
+        <v>24351.66091763923</v>
       </c>
       <c r="D123" t="n">
-        <v>41787.77777777777</v>
+        <v>13190.4165054401</v>
       </c>
       <c r="E123" t="n">
-        <v>35359.27777777778</v>
+        <v>11161.24441219914</v>
       </c>
       <c r="F123" t="n">
-        <v>5934.388888888889</v>
+        <v>1873.204685972249</v>
       </c>
       <c r="G123" t="n">
-        <v>67163.77777777777</v>
+        <v>21200.41433356218</v>
       </c>
       <c r="H123" t="n">
-        <v>9983.277777777777</v>
+        <v>3151.246584077057</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -5011,22 +5012,22 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>99252.11111111111</v>
+        <v>27217.46861485253</v>
       </c>
       <c r="D124" t="n">
-        <v>51827.38888888888</v>
+        <v>14212.39623703253</v>
       </c>
       <c r="E124" t="n">
-        <v>47424.72222222223</v>
+        <v>13005.07237782</v>
       </c>
       <c r="F124" t="n">
-        <v>7634.777777777777</v>
+        <v>2093.651431911733</v>
       </c>
       <c r="G124" t="n">
-        <v>65132.88888888889</v>
+        <v>17861.10480958378</v>
       </c>
       <c r="H124" t="n">
-        <v>34119.22222222222</v>
+        <v>9356.363805268747</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5048,22 +5049,22 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>36723.55555555555</v>
+        <v>8590.448998500913</v>
       </c>
       <c r="D125" t="n">
-        <v>19586.66666666665</v>
+        <v>4581.75300580838</v>
       </c>
       <c r="E125" t="n">
-        <v>17136.88888888891</v>
+        <v>4008.695992692533</v>
       </c>
       <c r="F125" t="n">
-        <v>2824.888888888889</v>
+        <v>660.8037691154549</v>
       </c>
       <c r="G125" t="n">
-        <v>20347.16666666666</v>
+        <v>4759.650716542759</v>
       </c>
       <c r="H125" t="n">
-        <v>16376.38888888889</v>
+        <v>3830.798281958154</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -5085,25 +5086,25 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>53245.11111111111</v>
+        <v>13294.12383661079</v>
       </c>
       <c r="D126" t="n">
-        <v>27991.16666666669</v>
+        <v>6988.773771574041</v>
       </c>
       <c r="E126" t="n">
-        <v>25253.94444444442</v>
+        <v>6305.350065036745</v>
       </c>
       <c r="F126" t="n">
-        <v>4095.777777777778</v>
+        <v>1022.624910508522</v>
       </c>
       <c r="G126" t="n">
-        <v>13413.83333333333</v>
+        <v>3349.136807788131</v>
       </c>
       <c r="H126" t="n">
-        <v>38927.05555555555</v>
+        <v>9719.222785924323</v>
       </c>
       <c r="I126" t="n">
-        <v>904.2222222222223</v>
+        <v>225.764242898333</v>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="n">
@@ -5122,19 +5123,19 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>207683.6666666667</v>
+        <v>49577.66666666675</v>
       </c>
       <c r="D127" t="n">
-        <v>105990.4444444444</v>
+        <v>25301.74379554093</v>
       </c>
       <c r="E127" t="n">
-        <v>101693.2222222223</v>
+        <v>24275.92287112582</v>
       </c>
       <c r="F127" t="n">
-        <v>15975.66666666667</v>
+        <v>3813.666666666673</v>
       </c>
       <c r="G127" t="n">
-        <v>207683.6666666667</v>
+        <v>49577.66666666675</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5159,19 +5160,19 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>153999.4444444444</v>
+        <v>32484.94616764271</v>
       </c>
       <c r="D128" t="n">
-        <v>80883.83333333334</v>
+        <v>17061.79513273372</v>
       </c>
       <c r="E128" t="n">
-        <v>73115.61111111109</v>
+        <v>15423.15103490899</v>
       </c>
       <c r="F128" t="n">
-        <v>11846.11111111111</v>
+        <v>2498.842012895593</v>
       </c>
       <c r="G128" t="n">
-        <v>153999.4444444444</v>
+        <v>32484.94616764271</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5196,22 +5197,22 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>188468.9444444444</v>
+        <v>44317.29673408238</v>
       </c>
       <c r="D129" t="n">
-        <v>96753.22222222222</v>
+        <v>22750.91671914561</v>
       </c>
       <c r="E129" t="n">
-        <v>91715.72222222222</v>
+        <v>21566.38001493677</v>
       </c>
       <c r="F129" t="n">
-        <v>14497.61111111111</v>
+        <v>3409.022825698645</v>
       </c>
       <c r="G129" t="n">
-        <v>188362.0555555556</v>
+        <v>44292.16247856656</v>
       </c>
       <c r="H129" t="n">
-        <v>106.8888888888889</v>
+        <v>25.13425551582902</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -5233,19 +5234,19 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>221816.8333333333</v>
+        <v>57814.04639397356</v>
       </c>
       <c r="D130" t="n">
-        <v>113843.8888888888</v>
+        <v>29672.120798884</v>
       </c>
       <c r="E130" t="n">
-        <v>107972.9444444445</v>
+        <v>28141.92559508955</v>
       </c>
       <c r="F130" t="n">
-        <v>17062.83333333333</v>
+        <v>4447.234337997966</v>
       </c>
       <c r="G130" t="n">
-        <v>221816.8333333333</v>
+        <v>57814.04639397356</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -5270,19 +5271,19 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>185794.5555555556</v>
+        <v>52567.77586313384</v>
       </c>
       <c r="D131" t="n">
-        <v>90987.00000000001</v>
+        <v>25743.40355753197</v>
       </c>
       <c r="E131" t="n">
-        <v>94807.55555555555</v>
+        <v>26824.37230560188</v>
       </c>
       <c r="F131" t="n">
-        <v>14291.88888888889</v>
+        <v>4043.675066394911</v>
       </c>
       <c r="G131" t="n">
-        <v>185794.5555555556</v>
+        <v>52567.77586313384</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -5307,22 +5308,22 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>185920.2222222222</v>
+        <v>49800.30456444387</v>
       </c>
       <c r="D132" t="n">
-        <v>96063.49999999991</v>
+        <v>25731.42125340381</v>
       </c>
       <c r="E132" t="n">
-        <v>89856.72222222231</v>
+        <v>24068.88331104006</v>
       </c>
       <c r="F132" t="n">
-        <v>14301.55555555555</v>
+        <v>3830.792658803374</v>
       </c>
       <c r="G132" t="n">
-        <v>185875.4444444444</v>
+        <v>49788.31045780824</v>
       </c>
       <c r="H132" t="n">
-        <v>44.77777777777778</v>
+        <v>11.99410663562441</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -5344,22 +5345,22 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>206286.8888888889</v>
+        <v>61048.21373329558</v>
       </c>
       <c r="D133" t="n">
-        <v>104689.7222222223</v>
+        <v>30981.70985235996</v>
       </c>
       <c r="E133" t="n">
-        <v>101597.1666666666</v>
+        <v>30066.50388093563</v>
       </c>
       <c r="F133" t="n">
-        <v>15868.22222222222</v>
+        <v>4696.016441022737</v>
       </c>
       <c r="G133" t="n">
-        <v>203713.6111111111</v>
+        <v>60286.68200135147</v>
       </c>
       <c r="H133" t="n">
-        <v>2573.277777777778</v>
+        <v>761.5317319441097</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -5381,22 +5382,22 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>200426.0555555556</v>
+        <v>55127.54714740149</v>
       </c>
       <c r="D134" t="n">
-        <v>99593.72222222226</v>
+        <v>27393.43246651336</v>
       </c>
       <c r="E134" t="n">
-        <v>100832.3333333333</v>
+        <v>27734.11468088813</v>
       </c>
       <c r="F134" t="n">
-        <v>15417.38888888889</v>
+        <v>4240.580549800115</v>
       </c>
       <c r="G134" t="n">
-        <v>199378.1111111111</v>
+        <v>54839.30814270305</v>
       </c>
       <c r="H134" t="n">
-        <v>1047.944444444444</v>
+        <v>288.239004698445</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
@@ -5418,22 +5419,22 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>201754.2222222222</v>
+        <v>60501.85590508967</v>
       </c>
       <c r="D135" t="n">
-        <v>105115.1111111112</v>
+        <v>31521.81518603903</v>
       </c>
       <c r="E135" t="n">
-        <v>96639.11111111105</v>
+        <v>28980.04071905063</v>
       </c>
       <c r="F135" t="n">
-        <v>15519.55555555555</v>
+        <v>4653.988915776128</v>
       </c>
       <c r="G135" t="n">
-        <v>183353.4444444444</v>
+        <v>54983.84892912431</v>
       </c>
       <c r="H135" t="n">
-        <v>18400.77777777778</v>
+        <v>5518.006975965357</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
@@ -5455,22 +5456,22 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>123277.5555555555</v>
+        <v>37489.33074255686</v>
       </c>
       <c r="D136" t="n">
-        <v>62812.38888888883</v>
+        <v>19101.56647066594</v>
       </c>
       <c r="E136" t="n">
-        <v>60465.16666666672</v>
+        <v>18387.76427189093</v>
       </c>
       <c r="F136" t="n">
-        <v>9482.888888888889</v>
+        <v>2883.794672504374</v>
       </c>
       <c r="G136" t="n">
-        <v>119805.1111111111</v>
+        <v>36433.34275126136</v>
       </c>
       <c r="H136" t="n">
-        <v>3472.444444444444</v>
+        <v>1055.987991295511</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
@@ -5492,22 +5493,22 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>130685.3888888889</v>
+        <v>39822.54911717057</v>
       </c>
       <c r="D137" t="n">
-        <v>64024.27777777772</v>
+        <v>19509.52564915004</v>
       </c>
       <c r="E137" t="n">
-        <v>66661.11111111118</v>
+        <v>20313.02346802053</v>
       </c>
       <c r="F137" t="n">
-        <v>10052.72222222222</v>
+        <v>3063.273009013121</v>
       </c>
       <c r="G137" t="n">
-        <v>127064.1666666667</v>
+        <v>38719.0875822989</v>
       </c>
       <c r="H137" t="n">
-        <v>3621.222222222222</v>
+        <v>1103.461534871667</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
@@ -5529,22 +5530,22 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>128068.0555555555</v>
+        <v>44109.72222222221</v>
       </c>
       <c r="D138" t="n">
-        <v>62360.99999999997</v>
+        <v>21478.63005780345</v>
       </c>
       <c r="E138" t="n">
-        <v>65707.05555555558</v>
+        <v>22631.09216441876</v>
       </c>
       <c r="F138" t="n">
-        <v>9851.388888888889</v>
+        <v>3393.055555555555</v>
       </c>
       <c r="G138" t="n">
-        <v>127076.4444444444</v>
+        <v>43768.1874774817</v>
       </c>
       <c r="H138" t="n">
-        <v>991.611111111111</v>
+        <v>341.5347447405109</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
@@ -5566,19 +5567,19 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>201762.8888888889</v>
+        <v>56136.16666666674</v>
       </c>
       <c r="D139" t="n">
-        <v>103794.1666666666</v>
+        <v>28878.4853900288</v>
       </c>
       <c r="E139" t="n">
-        <v>97968.72222222229</v>
+        <v>27257.68127663794</v>
       </c>
       <c r="F139" t="n">
-        <v>15520.22222222222</v>
+        <v>4318.166666666672</v>
       </c>
       <c r="G139" t="n">
-        <v>201762.8888888889</v>
+        <v>56136.16666666674</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -5603,22 +5604,22 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>116579.6666666667</v>
+        <v>30171.18172882335</v>
       </c>
       <c r="D140" t="n">
-        <v>60572.77777777775</v>
+        <v>15676.42401464777</v>
       </c>
       <c r="E140" t="n">
-        <v>56006.88888888891</v>
+        <v>14494.75771417558</v>
       </c>
       <c r="F140" t="n">
-        <v>8967.666666666666</v>
+        <v>2320.860132986411</v>
       </c>
       <c r="G140" t="n">
-        <v>115806.1666666667</v>
+        <v>29970.99751373228</v>
       </c>
       <c r="H140" t="n">
-        <v>773.4999999999999</v>
+        <v>200.1842150910667</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
@@ -5640,19 +5641,19 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>153035.2777777778</v>
+        <v>42826.13122317864</v>
       </c>
       <c r="D141" t="n">
-        <v>80146.44444444444</v>
+        <v>22428.56808371401</v>
       </c>
       <c r="E141" t="n">
-        <v>72888.83333333334</v>
+        <v>20397.56313946463</v>
       </c>
       <c r="F141" t="n">
-        <v>11771.94444444445</v>
+        <v>3294.317786398357</v>
       </c>
       <c r="G141" t="n">
-        <v>153035.2777777778</v>
+        <v>42826.13122317864</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -5677,22 +5678,22 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>108499.4444444445</v>
+        <v>28151.15255182493</v>
       </c>
       <c r="D142" t="n">
-        <v>57639.11111111117</v>
+        <v>14954.98357755473</v>
       </c>
       <c r="E142" t="n">
-        <v>50860.33333333328</v>
+        <v>13196.16897427021</v>
       </c>
       <c r="F142" t="n">
-        <v>8346.111111111111</v>
+        <v>2165.473273217302</v>
       </c>
       <c r="G142" t="n">
-        <v>106291.6111111111</v>
+        <v>27578.31042075305</v>
       </c>
       <c r="H142" t="n">
-        <v>2207.833333333333</v>
+        <v>572.8421310718819</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -5714,22 +5715,22 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>214523.1111111111</v>
+        <v>54940.16666666677</v>
       </c>
       <c r="D143" t="n">
-        <v>118013.2777777777</v>
+        <v>30223.63938509434</v>
       </c>
       <c r="E143" t="n">
-        <v>96509.83333333343</v>
+        <v>24716.52728157243</v>
       </c>
       <c r="F143" t="n">
-        <v>16501.77777777778</v>
+        <v>4226.166666666675</v>
       </c>
       <c r="G143" t="n">
-        <v>198627.7222222222</v>
+        <v>50869.29844988653</v>
       </c>
       <c r="H143" t="n">
-        <v>15895.38888888889</v>
+        <v>4070.868216780243</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -5751,22 +5752,22 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>169444.1666666667</v>
+        <v>48944.06916337048</v>
       </c>
       <c r="D144" t="n">
-        <v>93311.83333333327</v>
+        <v>26953.19003463813</v>
       </c>
       <c r="E144" t="n">
-        <v>76132.33333333339</v>
+        <v>21990.87912873235</v>
       </c>
       <c r="F144" t="n">
-        <v>13034.16666666667</v>
+        <v>3764.928397182344</v>
       </c>
       <c r="G144" t="n">
-        <v>158595.6666666667</v>
+        <v>45810.47215165773</v>
       </c>
       <c r="H144" t="n">
-        <v>10848.5</v>
+        <v>3133.597011712755</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -5788,22 +5789,22 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>138598.0555555556</v>
+        <v>35918.99999999994</v>
       </c>
       <c r="D145" t="n">
-        <v>75124.11111111112</v>
+        <v>19469.12556733797</v>
       </c>
       <c r="E145" t="n">
-        <v>63473.94444444444</v>
+        <v>16449.87443266197</v>
       </c>
       <c r="F145" t="n">
-        <v>10661.38888888889</v>
+        <v>2762.999999999995</v>
       </c>
       <c r="G145" t="n">
-        <v>126087.7222222222</v>
+        <v>32676.8285193194</v>
       </c>
       <c r="H145" t="n">
-        <v>12510.33333333333</v>
+        <v>3242.171480680539</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
@@ -5825,22 +5826,22 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>97216.16666666667</v>
+        <v>25360.29951364228</v>
       </c>
       <c r="D146" t="n">
-        <v>52730.16666666663</v>
+        <v>13755.45720349265</v>
       </c>
       <c r="E146" t="n">
-        <v>44486.00000000004</v>
+        <v>11604.84231014963</v>
       </c>
       <c r="F146" t="n">
-        <v>7478.166666666667</v>
+        <v>1950.792270280175</v>
       </c>
       <c r="G146" t="n">
-        <v>95728.38888888889</v>
+        <v>24972.19029942531</v>
       </c>
       <c r="H146" t="n">
-        <v>1487.777777777778</v>
+        <v>388.1092142169657</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -5862,22 +5863,22 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1914.611111111111</v>
+        <v>490.7847125816486</v>
       </c>
       <c r="D147" t="n">
-        <v>1038.825991727768</v>
+        <v>266.289019641478</v>
       </c>
       <c r="E147" t="n">
-        <v>875.7851193833433</v>
+        <v>224.4956929401706</v>
       </c>
       <c r="F147" t="n">
-        <v>147.2777777777778</v>
+        <v>37.75267019858835</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>1914.611111111111</v>
+        <v>490.7847125816486</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -5899,19 +5900,19 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>201803.3333333333</v>
+        <v>54794.99999999998</v>
       </c>
       <c r="D148" t="n">
-        <v>103298.7222222221</v>
+        <v>28048.36466609401</v>
       </c>
       <c r="E148" t="n">
-        <v>98504.61111111121</v>
+        <v>26746.63533390596</v>
       </c>
       <c r="F148" t="n">
-        <v>15523.33333333333</v>
+        <v>4214.999999999998</v>
       </c>
       <c r="G148" t="n">
-        <v>201803.3333333333</v>
+        <v>54794.99999999998</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -5936,19 +5937,19 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>203605.2777777778</v>
+        <v>57856.7052274807</v>
       </c>
       <c r="D149" t="n">
-        <v>109854.3333333334</v>
+        <v>31216.33118255923</v>
       </c>
       <c r="E149" t="n">
-        <v>93750.94444444437</v>
+        <v>26640.37404492147</v>
       </c>
       <c r="F149" t="n">
-        <v>15661.94444444445</v>
+        <v>4450.515786729285</v>
       </c>
       <c r="G149" t="n">
-        <v>203605.2777777778</v>
+        <v>57856.7052274807</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -5973,19 +5974,19 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>242273.0555555556</v>
+        <v>66899.44444444435</v>
       </c>
       <c r="D150" t="n">
-        <v>130397.9444444444</v>
+        <v>36007.09959275868</v>
       </c>
       <c r="E150" t="n">
-        <v>111875.1111111112</v>
+        <v>30892.34485168567</v>
       </c>
       <c r="F150" t="n">
-        <v>18636.38888888889</v>
+        <v>5146.111111111104</v>
       </c>
       <c r="G150" t="n">
-        <v>242273.0555555556</v>
+        <v>66899.44444444435</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6010,19 +6011,19 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>109192.7777777778</v>
+        <v>29013.49491288255</v>
       </c>
       <c r="D151" t="n">
-        <v>59427.33333333333</v>
+        <v>15790.3724810611</v>
       </c>
       <c r="E151" t="n">
-        <v>49765.44444444445</v>
+        <v>13223.12243182145</v>
       </c>
       <c r="F151" t="n">
-        <v>8399.444444444445</v>
+        <v>2231.807300990966</v>
       </c>
       <c r="G151" t="n">
-        <v>109192.7777777778</v>
+        <v>29013.49491288255</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6047,19 +6048,19 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>158613.7222222222</v>
+        <v>46691.96368010755</v>
       </c>
       <c r="D152" t="n">
-        <v>83555.33333333326</v>
+        <v>24596.62716831876</v>
       </c>
       <c r="E152" t="n">
-        <v>75058.38888888896</v>
+        <v>22095.33651178879</v>
       </c>
       <c r="F152" t="n">
-        <v>12201.05555555555</v>
+        <v>3591.689513854426</v>
       </c>
       <c r="G152" t="n">
-        <v>158613.7222222222</v>
+        <v>46691.96368010755</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -6084,19 +6085,19 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>179763.2777777778</v>
+        <v>45391.49154301149</v>
       </c>
       <c r="D153" t="n">
-        <v>96163.16666666673</v>
+        <v>24281.87570041518</v>
       </c>
       <c r="E153" t="n">
-        <v>83600.11111111105</v>
+        <v>21109.6158425963</v>
       </c>
       <c r="F153" t="n">
-        <v>13827.94444444445</v>
+        <v>3491.653195616268</v>
       </c>
       <c r="G153" t="n">
-        <v>179763.2777777778</v>
+        <v>45391.49154301149</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -6121,25 +6122,25 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>18415.94444444445</v>
+        <v>4678.663301158263</v>
       </c>
       <c r="D154" t="n">
-        <v>9734.424970129343</v>
+        <v>2473.079618751897</v>
       </c>
       <c r="E154" t="n">
-        <v>8681.519474315102</v>
+        <v>2205.583682406367</v>
       </c>
       <c r="F154" t="n">
-        <v>1416.611111111111</v>
+        <v>359.8971770121741</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>18355.27777777778</v>
+        <v>4663.250629394771</v>
       </c>
       <c r="I154" t="n">
-        <v>60.66666666666667</v>
+        <v>15.41267176349246</v>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="n">
@@ -6158,25 +6159,25 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>131960.1111111111</v>
+        <v>43368.74251495911</v>
       </c>
       <c r="D155" t="n">
-        <v>70703.38888888882</v>
+        <v>23236.69661868794</v>
       </c>
       <c r="E155" t="n">
-        <v>61256.72222222228</v>
+        <v>20132.04589627117</v>
       </c>
       <c r="F155" t="n">
-        <v>10150.77777777778</v>
+        <v>3336.057116535316</v>
       </c>
       <c r="G155" t="n">
-        <v>116273.4444444444</v>
+        <v>38213.31333369817</v>
       </c>
       <c r="H155" t="n">
-        <v>11016.05555555555</v>
+        <v>3620.430999160827</v>
       </c>
       <c r="I155" t="n">
-        <v>4670.61111111111</v>
+        <v>1534.998182100116</v>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="n">
@@ -6195,22 +6196,22 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>116701.7222222222</v>
+        <v>33646.79134794704</v>
       </c>
       <c r="D156" t="n">
-        <v>62044.66666666666</v>
+        <v>17888.37314338056</v>
       </c>
       <c r="E156" t="n">
-        <v>54657.05555555555</v>
+        <v>15758.41820456648</v>
       </c>
       <c r="F156" t="n">
-        <v>8977.055555555555</v>
+        <v>2588.21471907285</v>
       </c>
       <c r="G156" t="n">
-        <v>114623.8888888889</v>
+        <v>33047.72200011557</v>
       </c>
       <c r="H156" t="n">
-        <v>2077.833333333333</v>
+        <v>599.0693478314694</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -6232,19 +6233,19 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>130146.6111111111</v>
+        <v>34508.5</v>
       </c>
       <c r="D157" t="n">
-        <v>69991.27777777781</v>
+        <v>18558.2550984168</v>
       </c>
       <c r="E157" t="n">
-        <v>60155.3333333333</v>
+        <v>15950.2449015832</v>
       </c>
       <c r="F157" t="n">
-        <v>10011.27777777778</v>
+        <v>2654.5</v>
       </c>
       <c r="G157" t="n">
-        <v>130146.6111111111</v>
+        <v>34508.5</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -6269,25 +6270,25 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>177767.0555555556</v>
+        <v>53451.30309380783</v>
       </c>
       <c r="D158" t="n">
-        <v>92245.8333333334</v>
+        <v>27736.63534692434</v>
       </c>
       <c r="E158" t="n">
-        <v>85521.22222222216</v>
+        <v>25714.66774688349</v>
       </c>
       <c r="F158" t="n">
-        <v>13674.38888888889</v>
+        <v>4111.638699523679</v>
       </c>
       <c r="G158" t="n">
-        <v>172457.2777777778</v>
+        <v>51854.75000654545</v>
       </c>
       <c r="H158" t="n">
-        <v>4423.611111111111</v>
+        <v>1330.098974358281</v>
       </c>
       <c r="I158" t="n">
-        <v>886.1666666666667</v>
+        <v>266.4541129040998</v>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="n">
@@ -6306,25 +6307,25 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>162982.4444444444</v>
+        <v>51901.77777777772</v>
       </c>
       <c r="D159" t="n">
-        <v>84645.88888888888</v>
+        <v>26955.4928439615</v>
       </c>
       <c r="E159" t="n">
-        <v>78336.55555555556</v>
+        <v>24946.28493381622</v>
       </c>
       <c r="F159" t="n">
-        <v>12537.11111111111</v>
+        <v>3992.44444444444</v>
       </c>
       <c r="G159" t="n">
-        <v>158156.5555555556</v>
+        <v>50364.97291793445</v>
       </c>
       <c r="H159" t="n">
-        <v>4825.166666666666</v>
+        <v>1536.574868095312</v>
       </c>
       <c r="I159" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.229991747956191</v>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="n">
@@ -6343,25 +6344,25 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>121793.3888888889</v>
+        <v>38088.55555555557</v>
       </c>
       <c r="D160" t="n">
-        <v>63210.33333333328</v>
+        <v>19767.8241390284</v>
       </c>
       <c r="E160" t="n">
-        <v>58583.05555555561</v>
+        <v>18320.73141652717</v>
       </c>
       <c r="F160" t="n">
-        <v>9368.722222222223</v>
+        <v>2929.88888888889</v>
       </c>
       <c r="G160" t="n">
-        <v>91658.66666666666</v>
+        <v>28664.49689372242</v>
       </c>
       <c r="H160" t="n">
-        <v>28771.16666666666</v>
+        <v>8997.632712077819</v>
       </c>
       <c r="I160" t="n">
-        <v>1363.555555555556</v>
+        <v>426.425949755326</v>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="n">
@@ -6380,25 +6381,25 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>122280.1666666667</v>
+        <v>39399.38888888889</v>
       </c>
       <c r="D161" t="n">
-        <v>63913.77777777777</v>
+        <v>20593.39510788496</v>
       </c>
       <c r="E161" t="n">
-        <v>58366.38888888888</v>
+        <v>18805.99378100393</v>
       </c>
       <c r="F161" t="n">
-        <v>9406.166666666666</v>
+        <v>3030.722222222222</v>
       </c>
       <c r="G161" t="n">
-        <v>106093.7222222222</v>
+        <v>34184.0212885689</v>
       </c>
       <c r="H161" t="n">
-        <v>11674</v>
+        <v>3761.431460448524</v>
       </c>
       <c r="I161" t="n">
-        <v>4512.444444444443</v>
+        <v>1453.936139871466</v>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="n">
@@ -6417,29 +6418,29 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>181178.1111111111</v>
+        <v>43506.13744890183</v>
       </c>
       <c r="D162" t="n">
-        <v>97446.50876405578</v>
+        <v>23399.7428177439</v>
       </c>
       <c r="E162" t="n">
-        <v>83731.60234705532</v>
+        <v>20106.39463115793</v>
       </c>
       <c r="F162" t="n">
-        <v>13936.77777777778</v>
+        <v>3346.625957607834</v>
       </c>
       <c r="G162" t="n">
-        <v>7666.388888888889</v>
+        <v>1840.923093254829</v>
       </c>
       <c r="H162" t="n">
-        <v>100924.7777777778</v>
+        <v>24234.97643877686</v>
       </c>
       <c r="I162" t="n">
-        <v>832</v>
+        <v>199.787414359827</v>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="n">
-        <v>71754.94444444444</v>
+        <v>17230.45050251032</v>
       </c>
     </row>
     <row r="163">
@@ -6454,29 +6455,29 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>104615.3333333333</v>
+        <v>30159.69419859629</v>
       </c>
       <c r="D163" t="n">
-        <v>57238.27777777777</v>
+        <v>16501.29956314964</v>
       </c>
       <c r="E163" t="n">
-        <v>47377.05555555555</v>
+        <v>13658.39463544665</v>
       </c>
       <c r="F163" t="n">
-        <v>8047.333333333333</v>
+        <v>2319.976476815099</v>
       </c>
       <c r="G163" t="n">
-        <v>54989.27777777778</v>
+        <v>15852.93234878996</v>
       </c>
       <c r="H163" t="n">
-        <v>47262.94444444445</v>
+        <v>13625.49739078742</v>
       </c>
       <c r="I163" t="n">
-        <v>421.7777777777778</v>
+        <v>121.5948789935951</v>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="n">
-        <v>1941.333333333333</v>
+        <v>559.6695800253143</v>
       </c>
     </row>
     <row r="164">
@@ -6491,29 +6492,29 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>153089.4444444444</v>
+        <v>42926.81005444274</v>
       </c>
       <c r="D164" t="n">
-        <v>83668.7222222222</v>
+        <v>23460.99928290388</v>
       </c>
       <c r="E164" t="n">
-        <v>69420.72222222223</v>
+        <v>19465.81077153885</v>
       </c>
       <c r="F164" t="n">
-        <v>11776.11111111111</v>
+        <v>3302.06231188021</v>
       </c>
       <c r="G164" t="n">
-        <v>111001.2222222222</v>
+        <v>31125.12687883909</v>
       </c>
       <c r="H164" t="n">
-        <v>5826.888888888889</v>
+        <v>1633.879810913073</v>
       </c>
       <c r="I164" t="n">
-        <v>13491.11111111111</v>
+        <v>3782.954247379301</v>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="n">
-        <v>22770.22222222222</v>
+        <v>6384.849117311273</v>
       </c>
     </row>
     <row r="165">
@@ -6528,29 +6529,29 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>136289.1111111111</v>
+        <v>37394.50000000004</v>
       </c>
       <c r="D165" t="n">
-        <v>76404.61111111104</v>
+        <v>20963.61335767429</v>
       </c>
       <c r="E165" t="n">
-        <v>59884.50000000006</v>
+        <v>16430.88664232574</v>
       </c>
       <c r="F165" t="n">
-        <v>10483.77777777778</v>
+        <v>2876.500000000003</v>
       </c>
       <c r="G165" t="n">
-        <v>81113.5</v>
+        <v>22255.62079774045</v>
       </c>
       <c r="H165" t="n">
-        <v>5839.166666666666</v>
+        <v>1602.128857812071</v>
       </c>
       <c r="I165" t="n">
-        <v>6533.222222222222</v>
+        <v>1792.561242766604</v>
       </c>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="n">
-        <v>42803.22222222222</v>
+        <v>11744.18910168092</v>
       </c>
     </row>
     <row r="166">
@@ -6565,29 +6566,29 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>130769.8888888889</v>
+        <v>38527.66666666663</v>
       </c>
       <c r="D166" t="n">
-        <v>70953.27777777775</v>
+        <v>20904.38600473489</v>
       </c>
       <c r="E166" t="n">
-        <v>59816.61111111114</v>
+        <v>17623.28066193173</v>
       </c>
       <c r="F166" t="n">
-        <v>10059.22222222222</v>
+        <v>2963.666666666664</v>
       </c>
       <c r="G166" t="n">
-        <v>88726.44444444445</v>
+        <v>26140.74925901786</v>
       </c>
       <c r="H166" t="n">
-        <v>15132</v>
+        <v>4458.217843217386</v>
       </c>
       <c r="I166" t="n">
-        <v>206.5555555555556</v>
+        <v>60.85578002864511</v>
       </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="n">
-        <v>26704.88888888889</v>
+        <v>7867.843784402733</v>
       </c>
     </row>
     <row r="167">
@@ -6602,25 +6603,25 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>106614.4444444445</v>
+        <v>31819.45111693681</v>
       </c>
       <c r="D167" t="n">
-        <v>56800.61111111111</v>
+        <v>16952.33960163751</v>
       </c>
       <c r="E167" t="n">
-        <v>49813.83333333334</v>
+        <v>14867.1115152993</v>
       </c>
       <c r="F167" t="n">
-        <v>8201.111111111111</v>
+        <v>2447.650085918216</v>
       </c>
       <c r="G167" t="n">
-        <v>93013.55555555556</v>
+        <v>27760.21860485068</v>
       </c>
       <c r="H167" t="n">
-        <v>3624.833333333334</v>
+        <v>1081.844093997466</v>
       </c>
       <c r="I167" t="n">
-        <v>9976.055555555557</v>
+        <v>2977.388418088661</v>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="n">
@@ -6639,29 +6640,29 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>104416</v>
+        <v>32482.93953436905</v>
       </c>
       <c r="D168" t="n">
-        <v>56610.66666666665</v>
+        <v>17611.10234383288</v>
       </c>
       <c r="E168" t="n">
-        <v>47805.33333333335</v>
+        <v>14871.83719053617</v>
       </c>
       <c r="F168" t="n">
-        <v>8032</v>
+        <v>2498.687656489927</v>
       </c>
       <c r="G168" t="n">
-        <v>32673.33333333333</v>
+        <v>10164.39924008726</v>
       </c>
       <c r="H168" t="n">
-        <v>58689.94444444445</v>
+        <v>18257.94817522571</v>
       </c>
       <c r="I168" t="n">
-        <v>31.05555555555556</v>
+        <v>9.661122177801774</v>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="n">
-        <v>13021.66666666667</v>
+        <v>4050.930996878278</v>
       </c>
     </row>
     <row r="169">
@@ -6676,29 +6677,29 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>83941.72222222222</v>
+        <v>24549.65511352398</v>
       </c>
       <c r="D169" t="n">
-        <v>47559.05555555555</v>
+        <v>13909.15483390836</v>
       </c>
       <c r="E169" t="n">
-        <v>36382.66666666666</v>
+        <v>10640.50027961561</v>
       </c>
       <c r="F169" t="n">
-        <v>6457.055555555556</v>
+        <v>1888.435008732613</v>
       </c>
       <c r="G169" t="n">
-        <v>44296.05555555555</v>
+        <v>12954.85555918819</v>
       </c>
       <c r="H169" t="n">
-        <v>29510.72222222222</v>
+        <v>8630.726574665983</v>
       </c>
       <c r="I169" t="n">
-        <v>4760.888888888889</v>
+        <v>1392.372912562056</v>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="n">
-        <v>5374.055555555555</v>
+        <v>1571.700067107745</v>
       </c>
     </row>
     <row r="170">
@@ -6713,29 +6714,29 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>42010.94444444445</v>
+        <v>11948.80674407265</v>
       </c>
       <c r="D170" t="n">
-        <v>20388.01848989282</v>
+        <v>5798.786388924536</v>
       </c>
       <c r="E170" t="n">
-        <v>21622.92595455162</v>
+        <v>6150.020355148115</v>
       </c>
       <c r="F170" t="n">
-        <v>3231.611111111111</v>
+        <v>919.1389803132809</v>
       </c>
       <c r="G170" t="n">
-        <v>2789.222222222222</v>
+        <v>793.3141646858048</v>
       </c>
       <c r="H170" t="n">
-        <v>14658.22222222222</v>
+        <v>4169.110379715975</v>
       </c>
       <c r="I170" t="n">
-        <v>11520.16666666667</v>
+        <v>3276.580590601572</v>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="n">
-        <v>13043.33333333333</v>
+        <v>3709.8016090693</v>
       </c>
     </row>
     <row r="171">
@@ -6750,29 +6751,29 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>100768.7777777778</v>
+        <v>30416.57997791971</v>
       </c>
       <c r="D171" t="n">
-        <v>50924.84922067213</v>
+        <v>15371.42538931998</v>
       </c>
       <c r="E171" t="n">
-        <v>49843.92855710565</v>
+        <v>15045.15458859973</v>
       </c>
       <c r="F171" t="n">
-        <v>7751.444444444444</v>
+        <v>2339.736921378439</v>
       </c>
       <c r="G171" t="n">
-        <v>13542.38888888889</v>
+        <v>4087.706170649</v>
       </c>
       <c r="H171" t="n">
-        <v>54320.50000000001</v>
+        <v>16396.3865507452</v>
       </c>
       <c r="I171" t="n">
-        <v>3371.333333333333</v>
+        <v>1017.621055121835</v>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="n">
-        <v>29534.55555555555</v>
+        <v>8914.866201403671</v>
       </c>
     </row>
     <row r="172">
@@ -6787,22 +6788,22 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>121209.8333333333</v>
+        <v>30201.16666666672</v>
       </c>
       <c r="D172" t="n">
-        <v>65475.9444444445</v>
+        <v>16314.26969613916</v>
       </c>
       <c r="E172" t="n">
-        <v>55733.88888888885</v>
+        <v>13886.89697052755</v>
       </c>
       <c r="F172" t="n">
-        <v>9323.833333333334</v>
+        <v>2323.166666666671</v>
       </c>
       <c r="G172" t="n">
-        <v>108404.1111111111</v>
+        <v>27010.43749491054</v>
       </c>
       <c r="H172" t="n">
-        <v>12805.72222222222</v>
+        <v>3190.729171756178</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -6824,19 +6825,19 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>44462.88888888889</v>
+        <v>7413.972392333549</v>
       </c>
       <c r="D173" t="n">
-        <v>25848.33333333332</v>
+        <v>4310.08498345815</v>
       </c>
       <c r="E173" t="n">
-        <v>18614.55555555557</v>
+        <v>3103.887408875399</v>
       </c>
       <c r="F173" t="n">
-        <v>3420.222222222222</v>
+        <v>570.3055686410422</v>
       </c>
       <c r="G173" t="n">
-        <v>44462.88888888889</v>
+        <v>7413.972392333549</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -6861,22 +6862,22 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>77053.88888888889</v>
+        <v>17397.28498335812</v>
       </c>
       <c r="D174" t="n">
-        <v>43180.22222222222</v>
+        <v>9749.263047942777</v>
       </c>
       <c r="E174" t="n">
-        <v>33873.66666666667</v>
+        <v>7648.02193541534</v>
       </c>
       <c r="F174" t="n">
-        <v>5927.222222222223</v>
+        <v>1338.252691027547</v>
       </c>
       <c r="G174" t="n">
-        <v>65991.61111111111</v>
+        <v>14899.6355870689</v>
       </c>
       <c r="H174" t="n">
-        <v>11062.27777777778</v>
+        <v>2497.649396289215</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
@@ -6898,22 +6899,22 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>91843.55555555555</v>
+        <v>25783.33333333335</v>
       </c>
       <c r="D175" t="n">
-        <v>47605.27777777774</v>
+        <v>13364.27730770844</v>
       </c>
       <c r="E175" t="n">
-        <v>44238.27777777781</v>
+        <v>12419.05602562492</v>
       </c>
       <c r="F175" t="n">
-        <v>7064.888888888889</v>
+        <v>1983.333333333335</v>
       </c>
       <c r="G175" t="n">
-        <v>88353.05555555555</v>
+        <v>24803.44177256335</v>
       </c>
       <c r="H175" t="n">
-        <v>3490.5</v>
+        <v>979.8915607700059</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
@@ -6935,25 +6936,25 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>104397.2222222222</v>
+        <v>20435.56052506969</v>
       </c>
       <c r="D176" t="n">
-        <v>55297.66666666666</v>
+        <v>10824.41457739527</v>
       </c>
       <c r="E176" t="n">
-        <v>49099.55555555556</v>
+        <v>9611.145947674426</v>
       </c>
       <c r="F176" t="n">
-        <v>8030.555555555556</v>
+        <v>1571.96619423613</v>
       </c>
       <c r="G176" t="n">
-        <v>81759.88888888889</v>
+        <v>16004.34496576299</v>
       </c>
       <c r="H176" t="n">
-        <v>9062.444444444443</v>
+        <v>1773.956509640778</v>
       </c>
       <c r="I176" t="n">
-        <v>13574.88888888889</v>
+        <v>2657.259049665929</v>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="n">
@@ -6972,25 +6973,25 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>124153.6111111111</v>
+        <v>30063.24491284473</v>
       </c>
       <c r="D177" t="n">
-        <v>65279.50000000004</v>
+        <v>15807.14067617171</v>
       </c>
       <c r="E177" t="n">
-        <v>58874.11111111107</v>
+        <v>14256.10423667302</v>
       </c>
       <c r="F177" t="n">
-        <v>9550.277777777777</v>
+        <v>2312.557300988056</v>
       </c>
       <c r="G177" t="n">
-        <v>113789.7222222222</v>
+        <v>27553.67529881766</v>
       </c>
       <c r="H177" t="n">
-        <v>2446.166666666667</v>
+        <v>592.3283820703591</v>
       </c>
       <c r="I177" t="n">
-        <v>7917.722222222221</v>
+        <v>1917.241231956701</v>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="n">
@@ -7009,25 +7010,25 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>51633.83333333334</v>
+        <v>9900.192388932401</v>
       </c>
       <c r="D178" t="n">
-        <v>26931.66666666668</v>
+        <v>5163.836657900624</v>
       </c>
       <c r="E178" t="n">
-        <v>24702.16666666666</v>
+        <v>4736.355731031776</v>
       </c>
       <c r="F178" t="n">
-        <v>3971.833333333333</v>
+        <v>761.5532606871078</v>
       </c>
       <c r="G178" t="n">
-        <v>49303.22222222223</v>
+        <v>9453.324571956126</v>
       </c>
       <c r="H178" t="n">
-        <v>1326.722222222222</v>
+        <v>254.3836937667859</v>
       </c>
       <c r="I178" t="n">
-        <v>1003.888888888889</v>
+        <v>192.4841232094896</v>
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="n">
@@ -7046,25 +7047,25 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>11855.27777777778</v>
+        <v>3643.94645400225</v>
       </c>
       <c r="D179" t="n">
-        <v>6077.163621728037</v>
+        <v>1867.932514520829</v>
       </c>
       <c r="E179" t="n">
-        <v>5778.114156049741</v>
+        <v>1776.013939481421</v>
       </c>
       <c r="F179" t="n">
-        <v>911.9444444444445</v>
+        <v>280.3035733847885</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>5061.333333333333</v>
+        <v>1555.697639332791</v>
       </c>
       <c r="I179" t="n">
-        <v>6793.944444444445</v>
+        <v>2088.248814669459</v>
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="n">
@@ -7083,25 +7084,25 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>172593.0555555556</v>
+        <v>52532.05795537816</v>
       </c>
       <c r="D180" t="n">
-        <v>86433.38888888892</v>
+        <v>26307.68532242198</v>
       </c>
       <c r="E180" t="n">
-        <v>86159.66666666664</v>
+        <v>26224.37263295618</v>
       </c>
       <c r="F180" t="n">
-        <v>13276.38888888889</v>
+        <v>4040.92753502909</v>
       </c>
       <c r="G180" t="n">
-        <v>152445.2222222222</v>
+        <v>46399.67247245659</v>
       </c>
       <c r="H180" t="n">
-        <v>13414.55555555556</v>
+        <v>4082.981251022885</v>
       </c>
       <c r="I180" t="n">
-        <v>6733.277777777778</v>
+        <v>2049.404231898695</v>
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="n">
@@ -7120,25 +7121,25 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1733.333333333333</v>
+        <v>622.6019862260207</v>
       </c>
       <c r="D181" t="n">
-        <v>873.6607064366965</v>
+        <v>313.8132064125667</v>
       </c>
       <c r="E181" t="n">
-        <v>859.672626896637</v>
+        <v>308.788779813454</v>
       </c>
       <c r="F181" t="n">
-        <v>133.3333333333333</v>
+        <v>47.89246047892467</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>1160.611111111111</v>
+        <v>416.883913277173</v>
       </c>
       <c r="I181" t="n">
-        <v>572.7222222222223</v>
+        <v>205.7180729488477</v>
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="n">
@@ -7157,25 +7158,25 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>119035.9444444445</v>
+        <v>46382.99636000214</v>
       </c>
       <c r="D182" t="n">
-        <v>60543.88888888883</v>
+        <v>23591.25213027003</v>
       </c>
       <c r="E182" t="n">
-        <v>58492.05555555562</v>
+        <v>22791.74422973211</v>
       </c>
       <c r="F182" t="n">
-        <v>9156.611111111111</v>
+        <v>3567.922796923242</v>
       </c>
       <c r="G182" t="n">
-        <v>103208.4444444445</v>
+        <v>40215.72580727797</v>
       </c>
       <c r="H182" t="n">
-        <v>6635.777777777778</v>
+        <v>2585.666522401542</v>
       </c>
       <c r="I182" t="n">
-        <v>9191.722222222224</v>
+        <v>3581.604030322641</v>
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="n">
@@ -7194,22 +7195,22 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>157731.8888888889</v>
+        <v>50685.29748865966</v>
       </c>
       <c r="D183" t="n">
-        <v>78551.77777777774</v>
+        <v>25241.69496083561</v>
       </c>
       <c r="E183" t="n">
-        <v>79180.11111111117</v>
+        <v>25443.60252782405</v>
       </c>
       <c r="F183" t="n">
-        <v>12133.22222222222</v>
+        <v>3898.869037589205</v>
       </c>
       <c r="G183" t="n">
-        <v>155427.2777777778</v>
+        <v>49944.7376653723</v>
       </c>
       <c r="H183" t="n">
-        <v>2304.611111111111</v>
+        <v>740.5598232873606</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
@@ -7231,22 +7232,22 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>66902.33333333333</v>
+        <v>22015.50000000003</v>
       </c>
       <c r="D184" t="n">
-        <v>34294.72222222223</v>
+        <v>11285.33818576334</v>
       </c>
       <c r="E184" t="n">
-        <v>32607.6111111111</v>
+        <v>10730.16181423669</v>
       </c>
       <c r="F184" t="n">
-        <v>5146.333333333333</v>
+        <v>1693.500000000002</v>
       </c>
       <c r="G184" t="n">
-        <v>66352.72222222222</v>
+        <v>21834.63988924156</v>
       </c>
       <c r="H184" t="n">
-        <v>549.6111111111111</v>
+        <v>180.8601107584691</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -7268,22 +7269,22 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>69206.94444444445</v>
+        <v>22926.22222222225</v>
       </c>
       <c r="D185" t="n">
-        <v>34551.83333333336</v>
+        <v>11446.00466823204</v>
       </c>
       <c r="E185" t="n">
-        <v>34655.11111111109</v>
+        <v>11480.21755399021</v>
       </c>
       <c r="F185" t="n">
-        <v>5323.611111111111</v>
+        <v>1763.555555555557</v>
       </c>
       <c r="G185" t="n">
-        <v>68637.83333333334</v>
+        <v>22737.69247412821</v>
       </c>
       <c r="H185" t="n">
-        <v>569.1111111111112</v>
+        <v>188.5297480940374</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
@@ -7305,25 +7306,25 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>139061.7222222222</v>
+        <v>46838.52103537734</v>
       </c>
       <c r="D186" t="n">
-        <v>67441.11111111107</v>
+        <v>22715.39465316797</v>
       </c>
       <c r="E186" t="n">
-        <v>71620.61111111115</v>
+        <v>24123.12638220937</v>
       </c>
       <c r="F186" t="n">
-        <v>10697.05555555555</v>
+        <v>3602.963156567488</v>
       </c>
       <c r="G186" t="n">
-        <v>137313.9444444444</v>
+        <v>46249.83764428004</v>
       </c>
       <c r="H186" t="n">
-        <v>1606.944444444444</v>
+        <v>541.2481591700447</v>
       </c>
       <c r="I186" t="n">
-        <v>140.8333333333333</v>
+        <v>47.43523192726234</v>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="n">
@@ -7342,25 +7343,25 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>163121.1111111111</v>
+        <v>55255.52141996958</v>
       </c>
       <c r="D187" t="n">
-        <v>81863.1666666667</v>
+        <v>27730.26696817557</v>
       </c>
       <c r="E187" t="n">
-        <v>81257.94444444439</v>
+        <v>27525.254451794</v>
       </c>
       <c r="F187" t="n">
-        <v>12547.77777777778</v>
+        <v>4250.424724613044</v>
       </c>
       <c r="G187" t="n">
-        <v>144220.5555555555</v>
+        <v>48853.16157067973</v>
       </c>
       <c r="H187" t="n">
-        <v>13091</v>
+        <v>4434.435408033156</v>
       </c>
       <c r="I187" t="n">
-        <v>5809.555555555555</v>
+        <v>1967.924441256687</v>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="n">
@@ -7379,25 +7380,25 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>93872.27777777778</v>
+        <v>37658.83333333338</v>
       </c>
       <c r="D188" t="n">
-        <v>46425.16666666669</v>
+        <v>18624.42944136273</v>
       </c>
       <c r="E188" t="n">
-        <v>47447.11111111109</v>
+        <v>19034.40389197065</v>
       </c>
       <c r="F188" t="n">
-        <v>7220.944444444444</v>
+        <v>2896.833333333337</v>
       </c>
       <c r="G188" t="n">
-        <v>32273.22222222222</v>
+        <v>12947.08007057661</v>
       </c>
       <c r="H188" t="n">
-        <v>57132.83333333334</v>
+        <v>22920.03453303279</v>
       </c>
       <c r="I188" t="n">
-        <v>4466.222222222222</v>
+        <v>1791.718729723979</v>
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="n">
@@ -7416,25 +7417,25 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>956.9444444444445</v>
+        <v>349.2131761401195</v>
       </c>
       <c r="D189" t="n">
-        <v>491.4681532110608</v>
+        <v>179.3491312384303</v>
       </c>
       <c r="E189" t="n">
-        <v>465.4762912333837</v>
+        <v>169.8640449016893</v>
       </c>
       <c r="F189" t="n">
-        <v>73.61111111111111</v>
+        <v>26.86255201077843</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>913.6111111111111</v>
+        <v>333.3997492960386</v>
       </c>
       <c r="I189" t="n">
-        <v>43.33333333333333</v>
+        <v>15.81342684408088</v>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="n">
@@ -7453,25 +7454,25 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2046.777777777778</v>
+        <v>638.6111680634468</v>
       </c>
       <c r="D190" t="n">
-        <v>1052.960846321814</v>
+        <v>328.5322731638803</v>
       </c>
       <c r="E190" t="n">
-        <v>993.8169314559643</v>
+        <v>310.0788948995665</v>
       </c>
       <c r="F190" t="n">
-        <v>157.4444444444445</v>
+        <v>49.12393600488053</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>1220.555555555555</v>
+        <v>380.8231736158169</v>
       </c>
       <c r="I190" t="n">
-        <v>826.2222222222223</v>
+        <v>257.7879944476299</v>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="n">
@@ -7490,22 +7491,22 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3465.222222222222</v>
+        <v>1201.556578691344</v>
       </c>
       <c r="D191" t="n">
-        <v>1702.505452643147</v>
+        <v>590.3392324343902</v>
       </c>
       <c r="E191" t="n">
-        <v>1762.716769579075</v>
+        <v>611.217346256954</v>
       </c>
       <c r="F191" t="n">
-        <v>266.5555555555555</v>
+        <v>92.42742913010339</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>3465.222222222222</v>
+        <v>1201.556578691344</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
@@ -7527,25 +7528,25 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1334.666666666667</v>
+        <v>470.2795318005279</v>
       </c>
       <c r="D192" t="n">
-        <v>695.0877192982456</v>
+        <v>244.919226167739</v>
       </c>
       <c r="E192" t="n">
-        <v>639.5789473684212</v>
+        <v>225.3603056327889</v>
       </c>
       <c r="F192" t="n">
-        <v>102.6666666666667</v>
+        <v>36.17534860004061</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>1151.222222222222</v>
+        <v>405.6415442045679</v>
       </c>
       <c r="I192" t="n">
-        <v>183.4444444444445</v>
+        <v>64.63798759596</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="n">
@@ -7564,25 +7565,25 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>7770.388888888889</v>
+        <v>2597.787113808185</v>
       </c>
       <c r="D193" t="n">
-        <v>4072.428568870514</v>
+        <v>1361.489445302254</v>
       </c>
       <c r="E193" t="n">
-        <v>3697.960320018374</v>
+        <v>1236.297668505931</v>
       </c>
       <c r="F193" t="n">
-        <v>597.7222222222222</v>
+        <v>199.829777985245</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>4166.5</v>
+        <v>1392.939293573698</v>
       </c>
       <c r="I193" t="n">
-        <v>3603.888888888889</v>
+        <v>1204.847820234487</v>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="n">
@@ -7601,22 +7602,22 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>390.7222222222222</v>
+        <v>94.9999377956177</v>
       </c>
       <c r="D194" t="n">
-        <v>194.3540950744558</v>
+        <v>47.25512369730466</v>
       </c>
       <c r="E194" t="n">
-        <v>196.3681271477664</v>
+        <v>47.74481409831304</v>
       </c>
       <c r="F194" t="n">
-        <v>30.05555555555556</v>
+        <v>7.307687522739823</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>390.7222222222222</v>
+        <v>94.9999377956177</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
@@ -7638,25 +7639,25 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>548.1666666666666</v>
+        <v>173.9054539855772</v>
       </c>
       <c r="D195" t="n">
-        <v>269.3372506051362</v>
+        <v>85.44703589245375</v>
       </c>
       <c r="E195" t="n">
-        <v>278.8294160615304</v>
+        <v>88.45841809312347</v>
       </c>
       <c r="F195" t="n">
-        <v>42.16666666666666</v>
+        <v>13.37734261427517</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>260</v>
+        <v>82.48480030936469</v>
       </c>
       <c r="I195" t="n">
-        <v>288.1666666666666</v>
+        <v>91.42065367621252</v>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="n">
@@ -7675,25 +7676,25 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>730.8888888888889</v>
+        <v>279.2957342230835</v>
       </c>
       <c r="D196" t="n">
-        <v>370.608935140341</v>
+        <v>141.6213821597613</v>
       </c>
       <c r="E196" t="n">
-        <v>360.2799537485479</v>
+        <v>137.6743520633222</v>
       </c>
       <c r="F196" t="n">
-        <v>56.22222222222222</v>
+        <v>21.4842872479295</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>586.4444444444445</v>
+        <v>224.0989488035018</v>
       </c>
       <c r="I196" t="n">
-        <v>144.4444444444445</v>
+        <v>55.19678541958172</v>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="n">
@@ -7712,22 +7713,22 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>303.3333333333333</v>
+        <v>85.68265844107545</v>
       </c>
       <c r="D197" t="n">
-        <v>140.8283570662993</v>
+        <v>39.77982862855892</v>
       </c>
       <c r="E197" t="n">
-        <v>162.504976267034</v>
+        <v>45.90282981251652</v>
       </c>
       <c r="F197" t="n">
-        <v>23.33333333333333</v>
+        <v>6.590973726236573</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>303.3333333333333</v>
+        <v>85.68265844107545</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
@@ -7749,25 +7750,25 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>254045.2777777778</v>
+        <v>81520.34286429983</v>
       </c>
       <c r="D198" t="n">
-        <v>129234.4444444445</v>
+        <v>41469.91557230975</v>
       </c>
       <c r="E198" t="n">
-        <v>124810.8333333333</v>
+        <v>40050.42729199008</v>
       </c>
       <c r="F198" t="n">
-        <v>19541.94444444445</v>
+        <v>6270.795604946141</v>
       </c>
       <c r="G198" t="n">
-        <v>239589.2777777778</v>
+        <v>76881.57104080955</v>
       </c>
       <c r="H198" t="n">
-        <v>5052.666666666666</v>
+        <v>1621.345307610813</v>
       </c>
       <c r="I198" t="n">
-        <v>9403.333333333334</v>
+        <v>3017.426515879472</v>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="n">
@@ -7786,22 +7787,22 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>46563.11111111111</v>
+        <v>15120.67897538772</v>
       </c>
       <c r="D199" t="n">
-        <v>23004.22222222222</v>
+        <v>7470.27960547291</v>
       </c>
       <c r="E199" t="n">
-        <v>23558.88888888889</v>
+        <v>7650.399369914807</v>
       </c>
       <c r="F199" t="n">
-        <v>3581.777777777778</v>
+        <v>1163.129151952901</v>
       </c>
       <c r="G199" t="n">
-        <v>46084.27777777777</v>
+        <v>14965.18495999061</v>
       </c>
       <c r="H199" t="n">
-        <v>478.8333333333333</v>
+        <v>155.4940153971035</v>
       </c>
       <c r="I199" t="n">
         <v>0</v>
@@ -7823,25 +7824,25 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1419.888888888889</v>
+        <v>453.5865709747518</v>
       </c>
       <c r="D200" t="n">
-        <v>736.7806184100249</v>
+        <v>235.3661591976948</v>
       </c>
       <c r="E200" t="n">
-        <v>683.108270478864</v>
+        <v>218.220411777057</v>
       </c>
       <c r="F200" t="n">
-        <v>109.2222222222222</v>
+        <v>34.89127469036552</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>1141.111111111111</v>
+        <v>364.5304080061586</v>
       </c>
       <c r="I200" t="n">
-        <v>278.7777777777778</v>
+        <v>89.05616296859317</v>
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="n">
@@ -7860,25 +7861,25 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>4914</v>
+        <v>1759.521274287703</v>
       </c>
       <c r="D201" t="n">
-        <v>2514.261197305684</v>
+        <v>900.2637496490485</v>
       </c>
       <c r="E201" t="n">
-        <v>2399.738802694316</v>
+        <v>859.2575246386549</v>
       </c>
       <c r="F201" t="n">
-        <v>378</v>
+        <v>135.3477903298233</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>1664</v>
+        <v>595.8167278011271</v>
       </c>
       <c r="I201" t="n">
-        <v>3250</v>
+        <v>1163.704546486576</v>
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="n">
@@ -7897,25 +7898,25 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>141418.3333333333</v>
+        <v>41042.23484210114</v>
       </c>
       <c r="D202" t="n">
-        <v>68573.55555555553</v>
+        <v>19901.32329190449</v>
       </c>
       <c r="E202" t="n">
-        <v>72844.77777777781</v>
+        <v>21140.91155019666</v>
       </c>
       <c r="F202" t="n">
-        <v>10878.33333333333</v>
+        <v>3157.094987853934</v>
       </c>
       <c r="G202" t="n">
-        <v>138269.4444444445</v>
+        <v>40128.36862530138</v>
       </c>
       <c r="H202" t="n">
-        <v>2684.5</v>
+        <v>779.0919100561256</v>
       </c>
       <c r="I202" t="n">
-        <v>464.3888888888889</v>
+        <v>134.7743067436343</v>
       </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="n">
@@ -7934,22 +7935,22 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>88747.38888888889</v>
+        <v>28346.99153569192</v>
       </c>
       <c r="D203" t="n">
-        <v>46189.00000000003</v>
+        <v>14753.32636187565</v>
       </c>
       <c r="E203" t="n">
-        <v>42558.38888888886</v>
+        <v>13593.66517381627</v>
       </c>
       <c r="F203" t="n">
-        <v>6826.722222222223</v>
+        <v>2180.53781043784</v>
       </c>
       <c r="G203" t="n">
-        <v>88020.11111111111</v>
+        <v>28114.69019963148</v>
       </c>
       <c r="H203" t="n">
-        <v>727.2777777777778</v>
+        <v>232.3013360604305</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
@@ -7971,25 +7972,25 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>143915.0555555556</v>
+        <v>55160.72126258934</v>
       </c>
       <c r="D204" t="n">
-        <v>71572.2222222222</v>
+        <v>27432.67815103656</v>
       </c>
       <c r="E204" t="n">
-        <v>72342.83333333336</v>
+        <v>27728.04311155278</v>
       </c>
       <c r="F204" t="n">
-        <v>11070.38888888889</v>
+        <v>4243.132404814564</v>
       </c>
       <c r="G204" t="n">
-        <v>138950.5</v>
+        <v>53257.87333514004</v>
       </c>
       <c r="H204" t="n">
-        <v>3494.111111111111</v>
+        <v>1339.246184608627</v>
       </c>
       <c r="I204" t="n">
-        <v>1470.444444444444</v>
+        <v>563.6017428406705</v>
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="n">
@@ -8008,25 +8009,25 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>139778.1666666667</v>
+        <v>43061.00081121855</v>
       </c>
       <c r="D205" t="n">
-        <v>72543.61111111117</v>
+        <v>22348.27206135637</v>
       </c>
       <c r="E205" t="n">
-        <v>67234.55555555549</v>
+        <v>20712.72874986218</v>
       </c>
       <c r="F205" t="n">
-        <v>10752.16666666667</v>
+        <v>3312.384677786042</v>
       </c>
       <c r="G205" t="n">
-        <v>123497.8333333333</v>
+        <v>38045.57198144012</v>
       </c>
       <c r="H205" t="n">
-        <v>7608.61111111111</v>
+        <v>2343.959840374226</v>
       </c>
       <c r="I205" t="n">
-        <v>8671.722222222221</v>
+        <v>2671.468989404208</v>
       </c>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="n">
@@ -8045,25 +8046,25 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>123210.3888888889</v>
+        <v>36503.27777777773</v>
       </c>
       <c r="D206" t="n">
-        <v>60725.88888888892</v>
+        <v>17991.12891699898</v>
       </c>
       <c r="E206" t="n">
-        <v>62484.49999999997</v>
+        <v>18512.14886077875</v>
       </c>
       <c r="F206" t="n">
-        <v>9477.722222222223</v>
+        <v>2807.944444444441</v>
       </c>
       <c r="G206" t="n">
-        <v>103554.3888888889</v>
+        <v>30679.83679629485</v>
       </c>
       <c r="H206" t="n">
-        <v>11310.72222222222</v>
+        <v>3351.003424860503</v>
       </c>
       <c r="I206" t="n">
-        <v>8345.277777777779</v>
+        <v>2472.437556622382</v>
       </c>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="n">
@@ -8082,25 +8083,25 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>144882.1111111111</v>
+        <v>44514.88888888885</v>
       </c>
       <c r="D207" t="n">
-        <v>73963.50000000006</v>
+        <v>22725.2140314846</v>
       </c>
       <c r="E207" t="n">
-        <v>70918.61111111104</v>
+        <v>21789.67485740425</v>
       </c>
       <c r="F207" t="n">
-        <v>11144.77777777778</v>
+        <v>3424.222222222219</v>
       </c>
       <c r="G207" t="n">
-        <v>139120.2222222222</v>
+        <v>42744.55408556514</v>
       </c>
       <c r="H207" t="n">
-        <v>386.3888888888889</v>
+        <v>118.7176134091479</v>
       </c>
       <c r="I207" t="n">
-        <v>5375.5</v>
+        <v>1651.617189914557</v>
       </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="n">
@@ -8119,25 +8120,25 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>41920.66666666666</v>
+        <v>13723.43023516238</v>
       </c>
       <c r="D208" t="n">
-        <v>21531.61111111113</v>
+        <v>7048.732437476682</v>
       </c>
       <c r="E208" t="n">
-        <v>20389.05555555553</v>
+        <v>6674.697797685702</v>
       </c>
       <c r="F208" t="n">
-        <v>3224.666666666667</v>
+        <v>1055.648479627876</v>
       </c>
       <c r="G208" t="n">
-        <v>41207.83333333334</v>
+        <v>13490.07234042554</v>
       </c>
       <c r="H208" t="n">
-        <v>58.5</v>
+        <v>19.15095184770438</v>
       </c>
       <c r="I208" t="n">
-        <v>654.3333333333333</v>
+        <v>214.2069428891379</v>
       </c>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="n">
@@ -8156,19 +8157,19 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>59589.83333333333</v>
+        <v>20042.63180338067</v>
       </c>
       <c r="D209" t="n">
-        <v>32605.44444444443</v>
+        <v>10966.6176465043</v>
       </c>
       <c r="E209" t="n">
-        <v>26984.3888888889</v>
+        <v>9076.01415687637</v>
       </c>
       <c r="F209" t="n">
-        <v>4583.833333333333</v>
+        <v>1541.74090795236</v>
       </c>
       <c r="G209" t="n">
-        <v>59589.83333333333</v>
+        <v>20042.63180338067</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -8193,25 +8194,25 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>52221.72222222223</v>
+        <v>15948.33167525668</v>
       </c>
       <c r="D210" t="n">
-        <v>26156.72222222225</v>
+        <v>7988.171660873382</v>
       </c>
       <c r="E210" t="n">
-        <v>26064.99999999998</v>
+        <v>7960.160014383297</v>
       </c>
       <c r="F210" t="n">
-        <v>4017.055555555556</v>
+        <v>1226.794744250514</v>
       </c>
       <c r="G210" t="n">
-        <v>49628.22222222223</v>
+        <v>15156.28582843899</v>
       </c>
       <c r="H210" t="n">
-        <v>409.5000000000001</v>
+        <v>125.0598705501616</v>
       </c>
       <c r="I210" t="n">
-        <v>2184</v>
+        <v>666.9859762675287</v>
       </c>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="n">
@@ -8230,19 +8231,19 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>39036.83333333334</v>
+        <v>11630.58997866094</v>
       </c>
       <c r="D211" t="n">
-        <v>18827.61111111111</v>
+        <v>5609.477163303397</v>
       </c>
       <c r="E211" t="n">
-        <v>20209.22222222223</v>
+        <v>6021.11281535754</v>
       </c>
       <c r="F211" t="n">
-        <v>3002.833333333333</v>
+        <v>894.6607675893028</v>
       </c>
       <c r="G211" t="n">
-        <v>39036.83333333334</v>
+        <v>11630.58997866094</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -8267,22 +8268,22 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>31850.72222222222</v>
+        <v>12108.33011463844</v>
       </c>
       <c r="D212" t="n">
-        <v>16450.77777777776</v>
+        <v>6253.906790123448</v>
       </c>
       <c r="E212" t="n">
-        <v>15399.94444444446</v>
+        <v>5854.423324514994</v>
       </c>
       <c r="F212" t="n">
-        <v>2450.055555555556</v>
+        <v>931.4100088183417</v>
       </c>
       <c r="G212" t="n">
-        <v>31527.88888888889</v>
+        <v>11985.60220458553</v>
       </c>
       <c r="H212" t="n">
-        <v>322.8333333333333</v>
+        <v>122.72791005291</v>
       </c>
       <c r="I212" t="n">
         <v>0</v>
@@ -8304,19 +8305,19 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>48370.83333333334</v>
+        <v>18843.18094150203</v>
       </c>
       <c r="D213" t="n">
-        <v>22832.33333333333</v>
+        <v>8894.487828064879</v>
       </c>
       <c r="E213" t="n">
-        <v>25538.5</v>
+        <v>9948.693113437153</v>
       </c>
       <c r="F213" t="n">
-        <v>3720.833333333333</v>
+        <v>1449.475457038618</v>
       </c>
       <c r="G213" t="n">
-        <v>48370.83333333334</v>
+        <v>18843.18094150203</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -8341,16 +8342,16 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1278.333333333333</v>
+        <v>464.6643397905342</v>
       </c>
       <c r="D214" t="n">
-        <v>617.9268014160104</v>
+        <v>224.6116421529442</v>
       </c>
       <c r="E214" t="n">
-        <v>660.4065319173228</v>
+        <v>240.05269763759</v>
       </c>
       <c r="F214" t="n">
-        <v>98.33333333333333</v>
+        <v>35.74341075311801</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -8359,7 +8360,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>1278.333333333333</v>
+        <v>464.6643397905342</v>
       </c>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="n">
@@ -8378,22 +8379,22 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>78155.27777777778</v>
+        <v>27278.83749333879</v>
       </c>
       <c r="D215" t="n">
-        <v>36717.05555555558</v>
+        <v>12815.49525780947</v>
       </c>
       <c r="E215" t="n">
-        <v>41438.2222222222</v>
+        <v>14463.34223552932</v>
       </c>
       <c r="F215" t="n">
-        <v>6011.944444444444</v>
+        <v>2098.372114872214</v>
       </c>
       <c r="G215" t="n">
-        <v>77396.94444444445</v>
+        <v>27014.15349049255</v>
       </c>
       <c r="H215" t="n">
-        <v>758.3333333333334</v>
+        <v>264.6840028462387</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
@@ -8415,22 +8416,22 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>117329.3333333333</v>
+        <v>38246.48679548026</v>
       </c>
       <c r="D216" t="n">
-        <v>59674.33333333328</v>
+        <v>19452.3699830314</v>
       </c>
       <c r="E216" t="n">
-        <v>57655.00000000006</v>
+        <v>18794.11681244886</v>
       </c>
       <c r="F216" t="n">
-        <v>9025.333333333334</v>
+        <v>2942.037445806174</v>
       </c>
       <c r="G216" t="n">
-        <v>117137.2222222222</v>
+        <v>38183.86328211296</v>
       </c>
       <c r="H216" t="n">
-        <v>192.1111111111111</v>
+        <v>62.62351336729791</v>
       </c>
       <c r="I216" t="n">
         <v>0</v>
@@ -8452,22 +8453,22 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>179118.3333333333</v>
+        <v>55012.38888888888</v>
       </c>
       <c r="D217" t="n">
-        <v>92700.8333333333</v>
+        <v>28471.09058438502</v>
       </c>
       <c r="E217" t="n">
-        <v>86417.50000000004</v>
+        <v>26541.29830450386</v>
       </c>
       <c r="F217" t="n">
-        <v>13778.33333333333</v>
+        <v>4231.722222222222</v>
       </c>
       <c r="G217" t="n">
-        <v>179012.1666666667</v>
+        <v>54979.78205381503</v>
       </c>
       <c r="H217" t="n">
-        <v>106.1666666666667</v>
+        <v>32.60683507385454</v>
       </c>
       <c r="I217" t="n">
         <v>0</v>
@@ -8489,22 +8490,22 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>147465.5</v>
+        <v>42397.02639569787</v>
       </c>
       <c r="D218" t="n">
-        <v>77342.77777777782</v>
+        <v>22236.41320146775</v>
       </c>
       <c r="E218" t="n">
-        <v>70122.72222222218</v>
+        <v>20160.61319423013</v>
       </c>
       <c r="F218" t="n">
-        <v>11343.5</v>
+        <v>3261.30972274599</v>
       </c>
       <c r="G218" t="n">
-        <v>145169.5555555556</v>
+        <v>41736.93154494182</v>
       </c>
       <c r="H218" t="n">
-        <v>2295.944444444444</v>
+        <v>660.0948507560548</v>
       </c>
       <c r="I218" t="n">
         <v>0</v>
@@ -8526,22 +8527,22 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>78257.83333333333</v>
+        <v>23107.92651469706</v>
       </c>
       <c r="D219" t="n">
-        <v>40515.94444444447</v>
+        <v>11963.52399520097</v>
       </c>
       <c r="E219" t="n">
-        <v>37741.88888888885</v>
+        <v>11144.40251949609</v>
       </c>
       <c r="F219" t="n">
-        <v>6019.833333333333</v>
+        <v>1777.53280882285</v>
       </c>
       <c r="G219" t="n">
-        <v>73153.16666666666</v>
+        <v>21600.62357528494</v>
       </c>
       <c r="H219" t="n">
-        <v>5104.666666666666</v>
+        <v>1507.302939412117</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -8563,19 +8564,19 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>94418.27777777778</v>
+        <v>28897.55555555556</v>
       </c>
       <c r="D220" t="n">
-        <v>47168.33333333338</v>
+        <v>14436.28887376053</v>
       </c>
       <c r="E220" t="n">
-        <v>47249.9444444444</v>
+        <v>14461.26668179503</v>
       </c>
       <c r="F220" t="n">
-        <v>7262.944444444444</v>
+        <v>2222.888888888889</v>
       </c>
       <c r="G220" t="n">
-        <v>94418.27777777778</v>
+        <v>28897.55555555556</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -8600,19 +8601,19 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>93613</v>
+        <v>20794.06179649589</v>
       </c>
       <c r="D221" t="n">
-        <v>50014.61111111109</v>
+        <v>11109.64197464192</v>
       </c>
       <c r="E221" t="n">
-        <v>43598.38888888891</v>
+        <v>9684.419821853971</v>
       </c>
       <c r="F221" t="n">
-        <v>7201</v>
+        <v>1599.543215115069</v>
       </c>
       <c r="G221" t="n">
-        <v>93613</v>
+        <v>20794.06179649589</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -8637,19 +8638,19 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>184243.2222222222</v>
+        <v>53894.47732189419</v>
       </c>
       <c r="D222" t="n">
-        <v>95984.05555555549</v>
+        <v>28077.07357160183</v>
       </c>
       <c r="E222" t="n">
-        <v>88259.16666666673</v>
+        <v>25817.40375029236</v>
       </c>
       <c r="F222" t="n">
-        <v>14172.55555555555</v>
+        <v>4145.729024761092</v>
       </c>
       <c r="G222" t="n">
-        <v>184243.2222222222</v>
+        <v>53894.47732189419</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -8674,19 +8675,19 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>43410.61111111111</v>
+        <v>12761.15675177559</v>
       </c>
       <c r="D223" t="n">
-        <v>20443.94444444445</v>
+        <v>6009.783622082478</v>
       </c>
       <c r="E223" t="n">
-        <v>22966.66666666666</v>
+        <v>6751.373129693108</v>
       </c>
       <c r="F223" t="n">
-        <v>3339.277777777778</v>
+        <v>981.6274424442759</v>
       </c>
       <c r="G223" t="n">
-        <v>43410.61111111111</v>
+        <v>12761.15675177559</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -8711,19 +8712,19 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>98848.38888888889</v>
+        <v>30920.49999999999</v>
       </c>
       <c r="D224" t="n">
-        <v>50106.33333333332</v>
+        <v>15673.62804036034</v>
       </c>
       <c r="E224" t="n">
-        <v>48742.05555555557</v>
+        <v>15246.87195963965</v>
       </c>
       <c r="F224" t="n">
-        <v>7603.722222222223</v>
+        <v>2378.499999999999</v>
       </c>
       <c r="G224" t="n">
-        <v>98848.38888888889</v>
+        <v>30920.49999999999</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -8748,19 +8749,19 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>159010.2222222222</v>
+        <v>47818.1920262756</v>
       </c>
       <c r="D225" t="n">
-        <v>82186.00000000001</v>
+        <v>24715.30367638376</v>
       </c>
       <c r="E225" t="n">
-        <v>76824.2222222222</v>
+        <v>23102.88834989184</v>
       </c>
       <c r="F225" t="n">
-        <v>12231.55555555555</v>
+        <v>3678.322463559661</v>
       </c>
       <c r="G225" t="n">
-        <v>159010.2222222222</v>
+        <v>47818.1920262756</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -8785,19 +8786,19 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>241326.2222222222</v>
+        <v>78994.26359215302</v>
       </c>
       <c r="D226" t="n">
-        <v>124038.0555555556</v>
+        <v>40601.86566460667</v>
       </c>
       <c r="E226" t="n">
-        <v>117288.1666666666</v>
+        <v>38392.39792754635</v>
       </c>
       <c r="F226" t="n">
-        <v>18563.55555555555</v>
+        <v>6076.481814781001</v>
       </c>
       <c r="G226" t="n">
-        <v>241326.2222222222</v>
+        <v>78994.26359215302</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -8822,19 +8823,19 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>69235.11111111111</v>
+        <v>22028.72979147325</v>
       </c>
       <c r="D227" t="n">
-        <v>33989.94444444445</v>
+        <v>10814.67610548387</v>
       </c>
       <c r="E227" t="n">
-        <v>35245.16666666666</v>
+        <v>11214.05368598938</v>
       </c>
       <c r="F227" t="n">
-        <v>5325.777777777777</v>
+        <v>1694.517676267173</v>
       </c>
       <c r="G227" t="n">
-        <v>69235.11111111111</v>
+        <v>22028.72979147325</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -8846,6 +8847,2143 @@
       <c r="K227" t="n">
         <v>0</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C227"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">List of admin-pcode where MSNA data is representative at the unit of analysis of the HNO (e.g. if your analysis is conducted at admin 3, include the list of admin/pcode where the data is representative at admin 3) ----  Liste des codes admin où les données MSNA sont représentatives à l'unité d'analyse de l'HNO (par exemple, si votre analyse est effectuée à l'admin 3, incluez la liste des codes admin où les données sont représentatives à l'admin 3) </t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>List of admin-pcode where MSNA data is not representative at the unit of analysis of the HNO (e.g., if your analysis is conducted at admin 3, but in some admin 3 units the data is only representative at admin 2 -&gt; include these admin 3 units) ---- Liste des codes admin où les données MSNA ne sont pas représentatives à l'unité d'analyse de la HNO (par exemple, si votre analyse est effectuée à l'admin 3, mais que dans certaines unités de l'admin 3 les données ne sont représentatives qu'à l'admin 2 -&gt; inclure ces unités de l'admin 3).</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unique list of admin codes at one or more levels above OCHA's unit of analysis that are representative in the MSNA and present in the MSNA data. ---- Liste unique de codes administratifs à un ou plusieurs niveaux au-dessus de l'unité d'analyse d'OCHA qui sont représentatifs dans le MSNA et présents dans les données du MSNA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MMR001001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MMR017</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MMR001002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MMR007</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MMR001003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MMR008</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MMR001004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MMR004</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MMR001005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MMR001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MMR001006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MMR002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MMR001007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MMR003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MMR001008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MMR009</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MMR001009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MMR010</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MMR001010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MMR011</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MMR001011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MMR018</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MMR001012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MMR012</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MMR001013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MMR005</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MMR001014</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MMR016</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MMR001015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MMR015</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MMR001016</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MMR014</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MMR001017</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MMR006</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MMR001018</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MMR013</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MMR002001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MMR002002</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MMR002003</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MMR002004</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MMR002005</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MMR002006</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MMR002007</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MMR003001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MMR003002</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MMR003003</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MMR003004</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MMR003005</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MMR003006</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MMR003007</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MMR004001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MMR004002</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MMR004003</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MMR004004</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MMR004005</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MMR004006</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MMR004007</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MMR004008</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MMR004009</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MMR005001</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MMR005002</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MMR005003</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MMR005004</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MMR005005</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MMR005006</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MMR005007</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MMR005008</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MMR005009</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MMR005010</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MMR005011</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MMR005012</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MMR005013</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MMR005014</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MMR005015</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MMR005016</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MMR005017</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MMR005018</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MMR005019</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MMR005020</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MMR005021</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MMR005022</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MMR005023</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MMR005024</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MMR005025</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MMR005026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MMR005027</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MMR005028</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MMR005029</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MMR005030</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MMR005031</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MMR005032</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MMR005033</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MMR005034</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MMR006001</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MMR006002</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MMR006003</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MMR006004</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MMR006005</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MMR006006</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MMR006007</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MMR006008</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MMR006009</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MMR006010</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MMR007001</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MMR007004</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MMR007005</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MMR007006</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MMR007008</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MMR007009</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MMR007010</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MMR007011</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MMR007012</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MMR007013</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MMR007014</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MMR008002</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MMR008003</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>MMR008004</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MMR008007</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>MMR008008</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MMR008009</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MMR008010</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MMR008011</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MMR008012</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MMR008014</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>MMR009002</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MMR009003</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MMR009005</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MMR009006</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MMR009008</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>MMR009009</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>MMR009010</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>MMR009011</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>MMR009014</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>MMR009015</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>MMR009016</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>MMR009018</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>MMR009019</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>MMR009020</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>MMR009021</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>MMR009022</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MMR009023</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MMR009024</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>MMR009025</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>MMR010001</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>MMR010002</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>MMR010003</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>MMR010004</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>MMR010005</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>MMR010006</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>MMR010007</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>MMR010008</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>MMR010009</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>MMR010010</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>MMR010011</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>MMR010012</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MMR010013</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>MMR010014</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>MMR010015</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MMR010016</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>MMR010017</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>MMR010018</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>MMR010019</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>MMR010021</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>MMR010022</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>MMR010023</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>MMR010024</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>MMR010028</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>MMR010029</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>MMR010030</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>MMR010031</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>MMR011001</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>MMR011002</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>MMR011004</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>MMR011005</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>MMR011006</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MMR011007</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MMR011009</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>MMR011010</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>MMR012001</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MMR012002</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>MMR012003</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>MMR012004</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>MMR012005</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>MMR012006</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>MMR012007</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>MMR012008</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>MMR012009</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>MMR012010</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>MMR012011</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>MMR012012</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>MMR012013</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>MMR012014</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>MMR012015</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>MMR012016</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>MMR012017</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>MMR014001</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>MMR014002</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>MMR014003</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>MMR014004</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>MMR014005</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>MMR014006</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>MMR014007</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>MMR014008</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>MMR014009</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>MMR014010</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>MMR014011</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>MMR014012</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>MMR014013</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>MMR014015</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>MMR014016</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>MMR014018</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>MMR014019</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>MMR014020</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>MMR014021</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>MMR015001</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>MMR015002</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>MMR015003</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>MMR015004</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>MMR015009</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>MMR015010</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>MMR015011</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>MMR015012</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>MMR015013</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>MMR015014</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>MMR015015</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>MMR015016</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>MMR015017</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>MMR015018</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>MMR015019</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>MMR015020</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>MMR015021</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>MMR015022</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>MMR017003</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>MMR017005</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>MMR017006</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>MMR017010</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>MMR018001</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>MMR018002</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>MMR018003</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>MMR018004</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>MMR018005</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>MMR018006</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>MMR018007</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>MMR018008</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
